--- a/backend/script_metadata_manager/excel_databases/quarto_metadata.xlsx
+++ b/backend/script_metadata_manager/excel_databases/quarto_metadata.xlsx
@@ -161,7 +161,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -342,6 +342,15 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2292,9 +2301,10 @@
         </is>
       </c>
       <c r="F2" s="40" t="n"/>
-      <c r="G2" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A2,"/",2),4),MID(_xlfn.TEXTAFTER(A2,"/",2),6,2),MID(_xlfn.TEXTAFTER(A2,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G2" s="61" t="inlineStr">
+        <is>
+          <t>2017-10-23</t>
+        </is>
       </c>
       <c r="H2" s="40">
         <f>FALSE()</f>
@@ -2548,9 +2558,10 @@
         <f>IFERROR(VLOOKUP(A3, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G3" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A3,"/",2),4),MID(_xlfn.TEXTAFTER(A3,"/",2),6,2),MID(_xlfn.TEXTAFTER(A3,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G3" s="61" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
       </c>
       <c r="H3" s="52">
         <f>FALSE()</f>
@@ -2786,9 +2797,10 @@
           <t>plan de negocio completo</t>
         </is>
       </c>
-      <c r="G4" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A4,"/",2),4),MID(_xlfn.TEXTAFTER(A4,"/",2),6,2),MID(_xlfn.TEXTAFTER(A4,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G4" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
       </c>
       <c r="H4" s="52">
         <f>FALSE()</f>
@@ -3023,9 +3035,10 @@
         <f>IFERROR(VLOOKUP(A5, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G5" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A5,"/",2),4),MID(_xlfn.TEXTAFTER(A5,"/",2),6,2),MID(_xlfn.TEXTAFTER(A5,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G5" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-23</t>
+        </is>
       </c>
       <c r="H5" s="52">
         <f>FALSE()</f>
@@ -3176,9 +3189,10 @@
         <f>IFERROR(VLOOKUP(A6, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G6" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A6,"/",2),4),MID(_xlfn.TEXTAFTER(A6,"/",2),6,2),MID(_xlfn.TEXTAFTER(A6,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G6" s="61" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
       </c>
       <c r="H6" s="52">
         <f>FALSE()</f>
@@ -3326,9 +3340,10 @@
           <t>Un Análisis del Período 1980-2017</t>
         </is>
       </c>
-      <c r="G7" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A7,"/",2),4),MID(_xlfn.TEXTAFTER(A7,"/",2),6,2),MID(_xlfn.TEXTAFTER(A7,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G7" s="61" t="inlineStr">
+        <is>
+          <t>2017-12-30</t>
+        </is>
       </c>
       <c r="H7" s="40">
         <f>FALSE()</f>
@@ -3511,9 +3526,10 @@
           <t>Fundamentos esenciales</t>
         </is>
       </c>
-      <c r="G8" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A8,"/",2),4),MID(_xlfn.TEXTAFTER(A8,"/",2),6,2),MID(_xlfn.TEXTAFTER(A8,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G8" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
       </c>
       <c r="H8" s="52">
         <f>TRUE()</f>
@@ -3659,9 +3675,10 @@
         <f>IFERROR(VLOOKUP(A9, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G9" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A9,"/",2),4),MID(_xlfn.TEXTAFTER(A9,"/",2),6,2),MID(_xlfn.TEXTAFTER(A9,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G9" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-26</t>
+        </is>
       </c>
       <c r="H9" s="52">
         <f>TRUE()</f>
@@ -3807,9 +3824,10 @@
         <f>IFERROR(VLOOKUP(A10, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G10" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A10,"/",2),4),MID(_xlfn.TEXTAFTER(A10,"/",2),6,2),MID(_xlfn.TEXTAFTER(A10,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G10" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
       </c>
       <c r="H10" s="52">
         <f>TRUE()</f>
@@ -3955,9 +3973,10 @@
         <f>IFERROR(VLOOKUP(A11, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G11" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A11,"/",2),4),MID(_xlfn.TEXTAFTER(A11,"/",2),6,2),MID(_xlfn.TEXTAFTER(A11,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G11" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
       </c>
       <c r="H11" s="52">
         <f>TRUE()</f>
@@ -4104,9 +4123,10 @@
           <t>economía abierta</t>
         </is>
       </c>
-      <c r="G12" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A12,"/",2),4),MID(_xlfn.TEXTAFTER(A12,"/",2),6,2),MID(_xlfn.TEXTAFTER(A12,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G12" s="61" t="inlineStr">
+        <is>
+          <t>2021-12-20</t>
+        </is>
       </c>
       <c r="H12" s="52">
         <f>TRUE()</f>
@@ -4252,9 +4272,10 @@
         <f>IFERROR(VLOOKUP(A13, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G13" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A13,"/",2),4),MID(_xlfn.TEXTAFTER(A13,"/",2),6,2),MID(_xlfn.TEXTAFTER(A13,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G13" s="61" t="inlineStr">
+        <is>
+          <t>2021-12-27</t>
+        </is>
       </c>
       <c r="H13" s="52">
         <f>TRUE()</f>
@@ -4400,9 +4421,10 @@
         <f>IFERROR(VLOOKUP(A14, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G14" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A14,"/",2),4),MID(_xlfn.TEXTAFTER(A14,"/",2),6,2),MID(_xlfn.TEXTAFTER(A14,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G14" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
       </c>
       <c r="H14" s="52">
         <f>TRUE()</f>
@@ -4548,9 +4570,10 @@
         <f>IFERROR(VLOOKUP(A15, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G15" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A15,"/",2),4),MID(_xlfn.TEXTAFTER(A15,"/",2),6,2),MID(_xlfn.TEXTAFTER(A15,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G15" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
       </c>
       <c r="H15" s="52">
         <f>TRUE()</f>
@@ -4696,9 +4719,10 @@
         <f>IFERROR(VLOOKUP(A16, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G16" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A16,"/",2),4),MID(_xlfn.TEXTAFTER(A16,"/",2),6,2),MID(_xlfn.TEXTAFTER(A16,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G16" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-17</t>
+        </is>
       </c>
       <c r="H16" s="52">
         <f>TRUE()</f>
@@ -4844,9 +4868,10 @@
         <f>IFERROR(VLOOKUP(A17, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G17" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A17,"/",2),4),MID(_xlfn.TEXTAFTER(A17,"/",2),6,2),MID(_xlfn.TEXTAFTER(A17,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G17" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
       </c>
       <c r="H17" s="52">
         <f>TRUE()</f>
@@ -4992,9 +5017,10 @@
         <f>IFERROR(VLOOKUP(A18, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G18" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A18,"/",2),4),MID(_xlfn.TEXTAFTER(A18,"/",2),6,2),MID(_xlfn.TEXTAFTER(A18,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G18" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
       </c>
       <c r="H18" s="52">
         <f>TRUE()</f>
@@ -5141,9 +5167,10 @@
           <t>teoría y práctica</t>
         </is>
       </c>
-      <c r="G19" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A19,"/",2),4),MID(_xlfn.TEXTAFTER(A19,"/",2),6,2),MID(_xlfn.TEXTAFTER(A19,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G19" s="61" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
       </c>
       <c r="H19" s="52">
         <f>FALSE()</f>
@@ -5294,9 +5321,10 @@
         <f>IFERROR(VLOOKUP(A20, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G20" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A20,"/",2),4),MID(_xlfn.TEXTAFTER(A20,"/",2),6,2),MID(_xlfn.TEXTAFTER(A20,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G20" s="61" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
       </c>
       <c r="H20" s="40">
         <f>FALSE()</f>
@@ -5452,9 +5480,10 @@
         <f>IFERROR(VLOOKUP(A21, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G21" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A21,"/",2),4),MID(_xlfn.TEXTAFTER(A21,"/",2),6,2),MID(_xlfn.TEXTAFTER(A21,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
       </c>
       <c r="H21" s="40">
         <f>FALSE()</f>
@@ -5610,9 +5639,10 @@
         <f>IFERROR(VLOOKUP(A22, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G22" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A22,"/",2),4),MID(_xlfn.TEXTAFTER(A22,"/",2),6,2),MID(_xlfn.TEXTAFTER(A22,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G22" s="61" t="inlineStr">
+        <is>
+          <t>2017-05-21</t>
+        </is>
       </c>
       <c r="H22" s="40">
         <f>FALSE()</f>
@@ -5748,9 +5778,10 @@
         <f>IFERROR(VLOOKUP(A23, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G23" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A23,"/",2),4),MID(_xlfn.TEXTAFTER(A23,"/",2),6,2),MID(_xlfn.TEXTAFTER(A23,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G23" s="61" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
       </c>
       <c r="H23" s="40">
         <f>FALSE()</f>
@@ -5886,9 +5917,10 @@
         <f>IFERROR(VLOOKUP(A24, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G24" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A24,"/",2),4),MID(_xlfn.TEXTAFTER(A24,"/",2),6,2),MID(_xlfn.TEXTAFTER(A24,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G24" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-15</t>
+        </is>
       </c>
       <c r="H24" s="40">
         <f>TRUE()</f>
@@ -6034,9 +6066,10 @@
         <f>IFERROR(VLOOKUP(A25, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G25" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A25,"/",2),4),MID(_xlfn.TEXTAFTER(A25,"/",2),6,2),MID(_xlfn.TEXTAFTER(A25,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G25" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-16</t>
+        </is>
       </c>
       <c r="H25" s="40">
         <f>TRUE()</f>
@@ -6182,9 +6215,10 @@
         <f>IFERROR(VLOOKUP(A26, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G26" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A26,"/",2),4),MID(_xlfn.TEXTAFTER(A26,"/",2),6,2),MID(_xlfn.TEXTAFTER(A26,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G26" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-17</t>
+        </is>
       </c>
       <c r="H26" s="40">
         <f>TRUE()</f>
@@ -6330,9 +6364,10 @@
         <f>IFERROR(VLOOKUP(A27, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G27" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A27,"/",2),4),MID(_xlfn.TEXTAFTER(A27,"/",2),6,2),MID(_xlfn.TEXTAFTER(A27,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G27" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-18</t>
+        </is>
       </c>
       <c r="H27" s="40">
         <f>TRUE()</f>
@@ -6478,9 +6513,10 @@
         <f>IFERROR(VLOOKUP(A28, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G28" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A28,"/",2),4),MID(_xlfn.TEXTAFTER(A28,"/",2),6,2),MID(_xlfn.TEXTAFTER(A28,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G28" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-18</t>
+        </is>
       </c>
       <c r="H28" s="40">
         <f>TRUE()</f>
@@ -6626,9 +6662,10 @@
         <f>IFERROR(VLOOKUP(A29, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G29" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A29,"/",2),4),MID(_xlfn.TEXTAFTER(A29,"/",2),6,2),MID(_xlfn.TEXTAFTER(A29,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G29" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
       </c>
       <c r="H29" s="40">
         <f>TRUE()</f>
@@ -6774,9 +6811,10 @@
         <f>IFERROR(VLOOKUP(A30, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G30" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A30,"/",2),4),MID(_xlfn.TEXTAFTER(A30,"/",2),6,2),MID(_xlfn.TEXTAFTER(A30,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G30" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-20</t>
+        </is>
       </c>
       <c r="H30" s="40">
         <f>TRUE()</f>
@@ -6922,9 +6960,10 @@
         <f>IFERROR(VLOOKUP(A31, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G31" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A31,"/",2),4),MID(_xlfn.TEXTAFTER(A31,"/",2),6,2),MID(_xlfn.TEXTAFTER(A31,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G31" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-21</t>
+        </is>
       </c>
       <c r="H31" s="40">
         <f>TRUE()</f>
@@ -7070,9 +7109,10 @@
         <f>IFERROR(VLOOKUP(A32, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G32" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A32,"/",2),4),MID(_xlfn.TEXTAFTER(A32,"/",2),6,2),MID(_xlfn.TEXTAFTER(A32,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G32" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-22</t>
+        </is>
       </c>
       <c r="H32" s="40">
         <f>TRUE()</f>
@@ -7218,9 +7258,10 @@
         <f>IFERROR(VLOOKUP(A33, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G33" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A33,"/",2),4),MID(_xlfn.TEXTAFTER(A33,"/",2),6,2),MID(_xlfn.TEXTAFTER(A33,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G33" s="61" t="inlineStr">
+        <is>
+          <t>2020-02-23</t>
+        </is>
       </c>
       <c r="H33" s="40">
         <f>TRUE()</f>
@@ -7366,9 +7407,10 @@
         <f>IFERROR(VLOOKUP(A34, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G34" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A34,"/",2),4),MID(_xlfn.TEXTAFTER(A34,"/",2),6,2),MID(_xlfn.TEXTAFTER(A34,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G34" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
       </c>
       <c r="H34" s="40">
         <f>FALSE()</f>
@@ -7504,9 +7546,10 @@
         <f>IFERROR(VLOOKUP(A35, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G35" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A35,"/",2),4),MID(_xlfn.TEXTAFTER(A35,"/",2),6,2),MID(_xlfn.TEXTAFTER(A35,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G35" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
       </c>
       <c r="H35" s="40">
         <f>FALSE()</f>
@@ -7642,9 +7685,10 @@
         <f>IFERROR(VLOOKUP(A36, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G36" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A36,"/",2),4),MID(_xlfn.TEXTAFTER(A36,"/",2),6,2),MID(_xlfn.TEXTAFTER(A36,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G36" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
       </c>
       <c r="H36" s="40">
         <f>FALSE()</f>
@@ -7780,9 +7824,10 @@
         <f>IFERROR(VLOOKUP(A37, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G37" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A37,"/",2),4),MID(_xlfn.TEXTAFTER(A37,"/",2),6,2),MID(_xlfn.TEXTAFTER(A37,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G37" s="61" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
       </c>
       <c r="H37" s="40">
         <f>FALSE()</f>
@@ -7918,9 +7963,10 @@
         <f>IFERROR(VLOOKUP(A38, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G38" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A38,"/",2),4),MID(_xlfn.TEXTAFTER(A38,"/",2),6,2),MID(_xlfn.TEXTAFTER(A38,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G38" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
       </c>
       <c r="H38" s="40">
         <f>FALSE()</f>
@@ -8056,9 +8102,10 @@
         <f>IFERROR(VLOOKUP(A39, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G39" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A39,"/",2),4),MID(_xlfn.TEXTAFTER(A39,"/",2),6,2),MID(_xlfn.TEXTAFTER(A39,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G39" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
       </c>
       <c r="H39" s="40">
         <f>FALSE()</f>
@@ -8194,9 +8241,10 @@
         <f>IFERROR(VLOOKUP(A40, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G40" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A40,"/",2),4),MID(_xlfn.TEXTAFTER(A40,"/",2),6,2),MID(_xlfn.TEXTAFTER(A40,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G40" s="61" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
       </c>
       <c r="H40" s="40">
         <f>FALSE()</f>
@@ -8332,9 +8380,10 @@
         <f>IFERROR(VLOOKUP(A41, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G41" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A41,"/",2),4),MID(_xlfn.TEXTAFTER(A41,"/",2),6,2),MID(_xlfn.TEXTAFTER(A41,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G41" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
       </c>
       <c r="H41" s="40">
         <f>FALSE()</f>
@@ -8470,9 +8519,10 @@
         <f>IFERROR(VLOOKUP(A42, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G42" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A42,"/",2),4),MID(_xlfn.TEXTAFTER(A42,"/",2),6,2),MID(_xlfn.TEXTAFTER(A42,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G42" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
       </c>
       <c r="H42" s="40">
         <f>TRUE()</f>
@@ -8618,9 +8668,10 @@
         <f>IFERROR(VLOOKUP(A43, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G43" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A43,"/",2),4),MID(_xlfn.TEXTAFTER(A43,"/",2),6,2),MID(_xlfn.TEXTAFTER(A43,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G43" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-18</t>
+        </is>
       </c>
       <c r="H43" s="40">
         <f>FALSE()</f>
@@ -8756,9 +8807,10 @@
         <f>IFERROR(VLOOKUP(A44, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G44" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A44,"/",2),4),MID(_xlfn.TEXTAFTER(A44,"/",2),6,2),MID(_xlfn.TEXTAFTER(A44,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G44" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
       </c>
       <c r="H44" s="40">
         <f>FALSE()</f>
@@ -8894,9 +8946,10 @@
         <f>IFERROR(VLOOKUP(A45, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G45" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A45,"/",2),4),MID(_xlfn.TEXTAFTER(A45,"/",2),6,2),MID(_xlfn.TEXTAFTER(A45,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G45" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
       </c>
       <c r="H45" s="40">
         <f>FALSE()</f>
@@ -9032,9 +9085,10 @@
         <f>IFERROR(VLOOKUP(A46, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G46" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A46,"/",2),4),MID(_xlfn.TEXTAFTER(A46,"/",2),6,2),MID(_xlfn.TEXTAFTER(A46,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G46" s="61" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
       </c>
       <c r="H46" s="40">
         <f>FALSE()</f>
@@ -9170,9 +9224,10 @@
         <f>IFERROR(VLOOKUP(A47, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G47" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A47,"/",2),4),MID(_xlfn.TEXTAFTER(A47,"/",2),6,2),MID(_xlfn.TEXTAFTER(A47,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G47" s="61" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
       </c>
       <c r="H47" s="40">
         <f>FALSE()</f>
@@ -9308,9 +9363,10 @@
         <f>IFERROR(VLOOKUP(A48, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G48" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A48,"/",2),4),MID(_xlfn.TEXTAFTER(A48,"/",2),6,2),MID(_xlfn.TEXTAFTER(A48,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G48" s="61" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
       </c>
       <c r="H48" s="40">
         <f>FALSE()</f>
@@ -9451,9 +9507,10 @@
         <f>IFERROR(VLOOKUP(A49, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G49" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A49,"/",2),4),MID(_xlfn.TEXTAFTER(A49,"/",2),6,2),MID(_xlfn.TEXTAFTER(A49,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G49" s="61" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
       </c>
       <c r="H49" s="40">
         <f>FALSE()</f>
@@ -9597,9 +9654,10 @@
       </c>
       <c r="E50" s="40" t="n"/>
       <c r="F50" s="40" t="n"/>
-      <c r="G50" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A50,"/",2),4),MID(_xlfn.TEXTAFTER(A50,"/",2),6,2),MID(_xlfn.TEXTAFTER(A50,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G50" s="61" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
       </c>
       <c r="H50" s="40">
         <f>FALSE()</f>
@@ -9770,9 +9828,10 @@
       </c>
       <c r="E51" s="40" t="n"/>
       <c r="F51" s="40" t="n"/>
-      <c r="G51" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A51,"/",2),4),MID(_xlfn.TEXTAFTER(A51,"/",2),6,2),MID(_xlfn.TEXTAFTER(A51,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G51" s="61" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="H51" s="40">
         <f>FALSE()</f>
@@ -9943,9 +10002,10 @@
       </c>
       <c r="E52" s="40" t="n"/>
       <c r="F52" s="40" t="n"/>
-      <c r="G52" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A52,"/",2),4),MID(_xlfn.TEXTAFTER(A52,"/",2),6,2),MID(_xlfn.TEXTAFTER(A52,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G52" s="61" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="H52" s="40">
         <f>FALSE()</f>
@@ -10123,9 +10183,10 @@
         <f>IFERROR(VLOOKUP(A53, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G53" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A53,"/",2),4),MID(_xlfn.TEXTAFTER(A53,"/",2),6,2),MID(_xlfn.TEXTAFTER(A53,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G53" s="61" t="inlineStr">
+        <is>
+          <t>2015-05-14</t>
+        </is>
       </c>
       <c r="H53" s="40">
         <f>FALSE()</f>
@@ -10350,9 +10411,10 @@
         <f>IFERROR(VLOOKUP(A54, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G54" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A54,"/",2),4),MID(_xlfn.TEXTAFTER(A54,"/",2),6,2),MID(_xlfn.TEXTAFTER(A54,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G54" s="61" t="inlineStr">
+        <is>
+          <t>2017-05-23</t>
+        </is>
       </c>
       <c r="H54" s="40">
         <f>FALSE()</f>
@@ -10587,9 +10649,10 @@
         <f>IFERROR(VLOOKUP(A55, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G55" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A55,"/",2),4),MID(_xlfn.TEXTAFTER(A55,"/",2),6,2),MID(_xlfn.TEXTAFTER(A55,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G55" s="61" t="inlineStr">
+        <is>
+          <t>2018-04-23</t>
+        </is>
       </c>
       <c r="H55" s="40">
         <f>FALSE()</f>
@@ -10725,9 +10788,10 @@
         <f>IFERROR(VLOOKUP(A56, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G56" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A56,"/",2),4),MID(_xlfn.TEXTAFTER(A56,"/",2),6,2),MID(_xlfn.TEXTAFTER(A56,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G56" s="61" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
       </c>
       <c r="H56" s="40">
         <f>FALSE()</f>
@@ -10863,9 +10927,10 @@
         <f>IFERROR(VLOOKUP(A57, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G57" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A57,"/",2),4),MID(_xlfn.TEXTAFTER(A57,"/",2),6,2),MID(_xlfn.TEXTAFTER(A57,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G57" s="61" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
       </c>
       <c r="H57" s="40">
         <f>FALSE()</f>
@@ -11001,9 +11066,10 @@
         <f>IFERROR(VLOOKUP(A58, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G58" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A58,"/",2),4),MID(_xlfn.TEXTAFTER(A58,"/",2),6,2),MID(_xlfn.TEXTAFTER(A58,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G58" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
       </c>
       <c r="H58" s="40">
         <f>FALSE()</f>
@@ -11139,9 +11205,10 @@
         <f>IFERROR(VLOOKUP(A59, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G59" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A59,"/",2),4),MID(_xlfn.TEXTAFTER(A59,"/",2),6,2),MID(_xlfn.TEXTAFTER(A59,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G59" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
       </c>
       <c r="H59" s="40">
         <f>FALSE()</f>
@@ -11282,9 +11349,10 @@
         <f>IFERROR(VLOOKUP(A60, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G60" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A60,"/",2),4),MID(_xlfn.TEXTAFTER(A60,"/",2),6,2),MID(_xlfn.TEXTAFTER(A60,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G60" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
       </c>
       <c r="H60" s="40">
         <f>FALSE()</f>
@@ -11430,9 +11498,10 @@
         <f>IFERROR(VLOOKUP(A61, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G61" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A61,"/",2),4),MID(_xlfn.TEXTAFTER(A61,"/",2),6,2),MID(_xlfn.TEXTAFTER(A61,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G61" s="61" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
       </c>
       <c r="H61" s="40">
         <f>TRUE()</f>
@@ -11578,9 +11647,10 @@
         <f>IFERROR(VLOOKUP(A62, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G62" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A62,"/",2),4),MID(_xlfn.TEXTAFTER(A62,"/",2),6,2),MID(_xlfn.TEXTAFTER(A62,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G62" s="61" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
       </c>
       <c r="H62" s="40">
         <f>FALSE()</f>
@@ -11716,9 +11786,10 @@
         <f>IFERROR(VLOOKUP(A63, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G63" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A63,"/",2),4),MID(_xlfn.TEXTAFTER(A63,"/",2),6,2),MID(_xlfn.TEXTAFTER(A63,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G63" s="61" t="inlineStr">
+        <is>
+          <t>2018-12-26</t>
+        </is>
       </c>
       <c r="H63" s="40">
         <f>FALSE()</f>
@@ -11854,9 +11925,10 @@
         <f>IFERROR(VLOOKUP(A64, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G64" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A64,"/",2),4),MID(_xlfn.TEXTAFTER(A64,"/",2),6,2),MID(_xlfn.TEXTAFTER(A64,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G64" s="61" t="inlineStr">
+        <is>
+          <t>2019-12-30</t>
+        </is>
       </c>
       <c r="H64" s="40">
         <f>FALSE()</f>
@@ -11997,9 +12069,10 @@
         <f>IFERROR(VLOOKUP(A65, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G65" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A65,"/",2),4),MID(_xlfn.TEXTAFTER(A65,"/",2),6,2),MID(_xlfn.TEXTAFTER(A65,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G65" s="61" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
       </c>
       <c r="H65" s="40">
         <f>TRUE()</f>
@@ -12151,9 +12224,10 @@
           <t>mínimos cuadrados ordinarios</t>
         </is>
       </c>
-      <c r="G66" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A66,"/",2),4),MID(_xlfn.TEXTAFTER(A66,"/",2),6,2),MID(_xlfn.TEXTAFTER(A66,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G66" s="61" t="inlineStr">
+        <is>
+          <t>2021-03-08</t>
+        </is>
       </c>
       <c r="H66" s="40">
         <f>TRUE()</f>
@@ -12304,9 +12378,10 @@
         <f>IFERROR(VLOOKUP(A67, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G67" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A67,"/",2),4),MID(_xlfn.TEXTAFTER(A67,"/",2),6,2),MID(_xlfn.TEXTAFTER(A67,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G67" s="61" t="inlineStr">
+        <is>
+          <t>2021-03-15</t>
+        </is>
       </c>
       <c r="H67" s="40">
         <f>TRUE()</f>
@@ -12457,9 +12532,10 @@
         <f>IFERROR(VLOOKUP(A68, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G68" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A68,"/",2),4),MID(_xlfn.TEXTAFTER(A68,"/",2),6,2),MID(_xlfn.TEXTAFTER(A68,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G68" s="61" t="inlineStr">
+        <is>
+          <t>2021-03-22</t>
+        </is>
       </c>
       <c r="H68" s="40">
         <f>TRUE()</f>
@@ -12610,9 +12686,10 @@
         <f>IFERROR(VLOOKUP(A69, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G69" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A69,"/",2),4),MID(_xlfn.TEXTAFTER(A69,"/",2),6,2),MID(_xlfn.TEXTAFTER(A69,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G69" s="61" t="inlineStr">
+        <is>
+          <t>2021-03-29</t>
+        </is>
       </c>
       <c r="H69" s="40">
         <f>TRUE()</f>
@@ -12763,9 +12840,10 @@
         <f>IFERROR(VLOOKUP(A70, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G70" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A70,"/",2),4),MID(_xlfn.TEXTAFTER(A70,"/",2),6,2),MID(_xlfn.TEXTAFTER(A70,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G70" s="61" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
       </c>
       <c r="H70" s="40">
         <f>TRUE()</f>
@@ -12916,9 +12994,10 @@
         <f>IFERROR(VLOOKUP(A71, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G71" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A71,"/",2),4),MID(_xlfn.TEXTAFTER(A71,"/",2),6,2),MID(_xlfn.TEXTAFTER(A71,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G71" s="61" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
       </c>
       <c r="H71" s="40">
         <f>TRUE()</f>
@@ -13069,9 +13148,10 @@
         <f>IFERROR(VLOOKUP(A72, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G72" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A72,"/",2),4),MID(_xlfn.TEXTAFTER(A72,"/",2),6,2),MID(_xlfn.TEXTAFTER(A72,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G72" s="61" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
       </c>
       <c r="H72" s="40">
         <f>TRUE()</f>
@@ -13222,9 +13302,10 @@
         <f>IFERROR(VLOOKUP(A73, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G73" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A73,"/",2),4),MID(_xlfn.TEXTAFTER(A73,"/",2),6,2),MID(_xlfn.TEXTAFTER(A73,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G73" s="61" t="inlineStr">
+        <is>
+          <t>2021-05-03</t>
+        </is>
       </c>
       <c r="H73" s="40">
         <f>TRUE()</f>
@@ -13375,9 +13456,10 @@
         <f>IFERROR(VLOOKUP(A74, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G74" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A74,"/",2),4),MID(_xlfn.TEXTAFTER(A74,"/",2),6,2),MID(_xlfn.TEXTAFTER(A74,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G74" s="61" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
       </c>
       <c r="H74" s="40">
         <f>TRUE()</f>
@@ -13529,9 +13611,10 @@
           <t>causas y consecuencias</t>
         </is>
       </c>
-      <c r="G75" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A75,"/",2),4),MID(_xlfn.TEXTAFTER(A75,"/",2),6,2),MID(_xlfn.TEXTAFTER(A75,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G75" s="61" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
       </c>
       <c r="H75" s="40">
         <f>TRUE()</f>
@@ -13682,9 +13765,10 @@
         <f>IFERROR(VLOOKUP(A76, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G76" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A76,"/",2),4),MID(_xlfn.TEXTAFTER(A76,"/",2),6,2),MID(_xlfn.TEXTAFTER(A76,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G76" s="61" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
       </c>
       <c r="H76" s="40">
         <f>TRUE()</f>
@@ -13835,9 +13919,10 @@
         <f>IFERROR(VLOOKUP(A77, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G77" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A77,"/",2),4),MID(_xlfn.TEXTAFTER(A77,"/",2),6,2),MID(_xlfn.TEXTAFTER(A77,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G77" s="61" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
       </c>
       <c r="H77" s="40">
         <f>TRUE()</f>
@@ -13988,9 +14073,10 @@
         <f>IFERROR(VLOOKUP(A78, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G78" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A78,"/",2),4),MID(_xlfn.TEXTAFTER(A78,"/",2),6,2),MID(_xlfn.TEXTAFTER(A78,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G78" s="61" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
       </c>
       <c r="H78" s="40">
         <f>TRUE()</f>
@@ -14141,9 +14227,10 @@
         <f>IFERROR(VLOOKUP(A79, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G79" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A79,"/",2),4),MID(_xlfn.TEXTAFTER(A79,"/",2),6,2),MID(_xlfn.TEXTAFTER(A79,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G79" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
       </c>
       <c r="H79" s="40">
         <f>TRUE()</f>
@@ -14294,9 +14381,10 @@
         <f>IFERROR(VLOOKUP(A80, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G80" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A80,"/",2),4),MID(_xlfn.TEXTAFTER(A80,"/",2),6,2),MID(_xlfn.TEXTAFTER(A80,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G80" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
       </c>
       <c r="H80" s="40">
         <f>TRUE()</f>
@@ -14447,9 +14535,10 @@
         <f>IFERROR(VLOOKUP(A81, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G81" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A81,"/",2),4),MID(_xlfn.TEXTAFTER(A81,"/",2),6,2),MID(_xlfn.TEXTAFTER(A81,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G81" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
       </c>
       <c r="H81" s="40">
         <f>TRUE()</f>
@@ -14600,9 +14689,10 @@
         <f>IFERROR(VLOOKUP(A82, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G82" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A82,"/",2),4),MID(_xlfn.TEXTAFTER(A82,"/",2),6,2),MID(_xlfn.TEXTAFTER(A82,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G82" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-25</t>
+        </is>
       </c>
       <c r="H82" s="40">
         <f>TRUE()</f>
@@ -14753,9 +14843,10 @@
         <f>IFERROR(VLOOKUP(A83, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G83" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A83,"/",2),4),MID(_xlfn.TEXTAFTER(A83,"/",2),6,2),MID(_xlfn.TEXTAFTER(A83,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G83" s="61" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
       </c>
       <c r="H83" s="40">
         <f>TRUE()</f>
@@ -14906,9 +14997,10 @@
         <f>IFERROR(VLOOKUP(A84, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G84" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A84,"/",2),4),MID(_xlfn.TEXTAFTER(A84,"/",2),6,2),MID(_xlfn.TEXTAFTER(A84,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G84" s="61" t="inlineStr">
+        <is>
+          <t>2021-11-08</t>
+        </is>
       </c>
       <c r="H84" s="40">
         <f>TRUE()</f>
@@ -15059,9 +15151,10 @@
         <f>IFERROR(VLOOKUP(A85, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G85" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A85,"/",2),4),MID(_xlfn.TEXTAFTER(A85,"/",2),6,2),MID(_xlfn.TEXTAFTER(A85,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G85" s="61" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
       </c>
       <c r="H85" s="40">
         <f>TRUE()</f>
@@ -15212,9 +15305,10 @@
         <f>IFERROR(VLOOKUP(A86, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G86" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A86,"/",2),4),MID(_xlfn.TEXTAFTER(A86,"/",2),6,2),MID(_xlfn.TEXTAFTER(A86,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G86" s="61" t="inlineStr">
+        <is>
+          <t>2021-11-22</t>
+        </is>
       </c>
       <c r="H86" s="40">
         <f>TRUE()</f>
@@ -15365,9 +15459,10 @@
         <f>IFERROR(VLOOKUP(A87, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G87" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A87,"/",2),4),MID(_xlfn.TEXTAFTER(A87,"/",2),6,2),MID(_xlfn.TEXTAFTER(A87,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G87" s="61" t="inlineStr">
+        <is>
+          <t>2021-11-29</t>
+        </is>
       </c>
       <c r="H87" s="40">
         <f>TRUE()</f>
@@ -15518,9 +15613,10 @@
         <f>IFERROR(VLOOKUP(A88, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G88" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A88,"/",2),4),MID(_xlfn.TEXTAFTER(A88,"/",2),6,2),MID(_xlfn.TEXTAFTER(A88,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G88" s="61" t="inlineStr">
+        <is>
+          <t>2021-12-06</t>
+        </is>
       </c>
       <c r="H88" s="40">
         <f>TRUE()</f>
@@ -15666,9 +15762,10 @@
         <f>IFERROR(VLOOKUP(A89, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G89" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A89,"/",2),4),MID(_xlfn.TEXTAFTER(A89,"/",2),6,2),MID(_xlfn.TEXTAFTER(A89,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G89" s="61" t="inlineStr">
+        <is>
+          <t>2022-01-11</t>
+        </is>
       </c>
       <c r="H89" s="40">
         <f>FALSE()</f>
@@ -15814,9 +15911,10 @@
         <f>IFERROR(VLOOKUP(A90, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G90" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A90,"/",2),4),MID(_xlfn.TEXTAFTER(A90,"/",2),6,2),MID(_xlfn.TEXTAFTER(A90,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G90" s="61" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
       </c>
       <c r="H90" s="40">
         <f>TRUE()</f>
@@ -15967,9 +16065,10 @@
         <f>IFERROR(VLOOKUP(A91, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G91" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A91,"/",2),4),MID(_xlfn.TEXTAFTER(A91,"/",2),6,2),MID(_xlfn.TEXTAFTER(A91,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G91" s="61" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
       </c>
       <c r="H91" s="40">
         <f>TRUE()</f>
@@ -16120,9 +16219,10 @@
         <f>IFERROR(VLOOKUP(A92, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G92" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A92,"/",2),4),MID(_xlfn.TEXTAFTER(A92,"/",2),6,2),MID(_xlfn.TEXTAFTER(A92,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G92" s="61" t="inlineStr">
+        <is>
+          <t>2022-03-14</t>
+        </is>
       </c>
       <c r="H92" s="40">
         <f>TRUE()</f>
@@ -16273,9 +16373,10 @@
         <f>IFERROR(VLOOKUP(A93, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G93" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A93,"/",2),4),MID(_xlfn.TEXTAFTER(A93,"/",2),6,2),MID(_xlfn.TEXTAFTER(A93,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G93" s="61" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
       </c>
       <c r="H93" s="40">
         <f>TRUE()</f>
@@ -16426,9 +16527,10 @@
         <f>IFERROR(VLOOKUP(A94, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G94" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A94,"/",2),4),MID(_xlfn.TEXTAFTER(A94,"/",2),6,2),MID(_xlfn.TEXTAFTER(A94,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G94" s="61" t="inlineStr">
+        <is>
+          <t>2022-03-21</t>
+        </is>
       </c>
       <c r="H94" s="40">
         <f>TRUE()</f>
@@ -16579,9 +16681,10 @@
         <f>IFERROR(VLOOKUP(A95, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G95" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A95,"/",2),4),MID(_xlfn.TEXTAFTER(A95,"/",2),6,2),MID(_xlfn.TEXTAFTER(A95,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G95" s="61" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
       </c>
       <c r="H95" s="40">
         <f>TRUE()</f>
@@ -16732,9 +16835,10 @@
         <f>IFERROR(VLOOKUP(A96, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G96" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A96,"/",2),4),MID(_xlfn.TEXTAFTER(A96,"/",2),6,2),MID(_xlfn.TEXTAFTER(A96,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G96" s="61" t="inlineStr">
+        <is>
+          <t>2022-04-04</t>
+        </is>
       </c>
       <c r="H96" s="40">
         <f>TRUE()</f>
@@ -16885,9 +16989,10 @@
         <f>IFERROR(VLOOKUP(A97, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G97" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A97,"/",2),4),MID(_xlfn.TEXTAFTER(A97,"/",2),6,2),MID(_xlfn.TEXTAFTER(A97,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G97" s="61" t="inlineStr">
+        <is>
+          <t>2022-04-11</t>
+        </is>
       </c>
       <c r="H97" s="40">
         <f>TRUE()</f>
@@ -17038,9 +17143,10 @@
         <f>IFERROR(VLOOKUP(A98, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G98" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A98,"/",2),4),MID(_xlfn.TEXTAFTER(A98,"/",2),6,2),MID(_xlfn.TEXTAFTER(A98,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G98" s="61" t="inlineStr">
+        <is>
+          <t>2022-04-18</t>
+        </is>
       </c>
       <c r="H98" s="40">
         <f>TRUE()</f>
@@ -17191,9 +17297,10 @@
         <f>IFERROR(VLOOKUP(A99, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G99" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A99,"/",2),4),MID(_xlfn.TEXTAFTER(A99,"/",2),6,2),MID(_xlfn.TEXTAFTER(A99,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G99" s="61" t="inlineStr">
+        <is>
+          <t>2022-04-25</t>
+        </is>
       </c>
       <c r="H99" s="40">
         <f>TRUE()</f>
@@ -17345,9 +17452,10 @@
           <t>diferencias clave</t>
         </is>
       </c>
-      <c r="G100" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A100,"/",2),4),MID(_xlfn.TEXTAFTER(A100,"/",2),6,2),MID(_xlfn.TEXTAFTER(A100,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G100" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
       </c>
       <c r="H100" s="40">
         <f>TRUE()</f>
@@ -17498,9 +17606,10 @@
         <f>IFERROR(VLOOKUP(A101, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G101" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A101,"/",2),4),MID(_xlfn.TEXTAFTER(A101,"/",2),6,2),MID(_xlfn.TEXTAFTER(A101,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G101" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
       </c>
       <c r="H101" s="40">
         <f>TRUE()</f>
@@ -17651,9 +17760,10 @@
         <f>IFERROR(VLOOKUP(A102, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G102" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A102,"/",2),4),MID(_xlfn.TEXTAFTER(A102,"/",2),6,2),MID(_xlfn.TEXTAFTER(A102,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G102" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
       </c>
       <c r="H102" s="40">
         <f>TRUE()</f>
@@ -17804,9 +17914,10 @@
         <f>IFERROR(VLOOKUP(A103, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G103" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A103,"/",2),4),MID(_xlfn.TEXTAFTER(A103,"/",2),6,2),MID(_xlfn.TEXTAFTER(A103,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G103" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
       </c>
       <c r="H103" s="40">
         <f>TRUE()</f>
@@ -17957,9 +18068,10 @@
         <f>IFERROR(VLOOKUP(A104, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G104" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A104,"/",2),4),MID(_xlfn.TEXTAFTER(A104,"/",2),6,2),MID(_xlfn.TEXTAFTER(A104,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G104" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
       </c>
       <c r="H104" s="40">
         <f>TRUE()</f>
@@ -18110,9 +18222,10 @@
         <f>IFERROR(VLOOKUP(A105, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G105" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A105,"/",2),4),MID(_xlfn.TEXTAFTER(A105,"/",2),6,2),MID(_xlfn.TEXTAFTER(A105,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G105" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
       </c>
       <c r="H105" s="40">
         <f>TRUE()</f>
@@ -18264,9 +18377,10 @@
           <t>teoría y práctica</t>
         </is>
       </c>
-      <c r="G106" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A106,"/",2),4),MID(_xlfn.TEXTAFTER(A106,"/",2),6,2),MID(_xlfn.TEXTAFTER(A106,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G106" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
       </c>
       <c r="H106" s="40">
         <f>TRUE()</f>
@@ -18417,9 +18531,10 @@
         <f>IFERROR(VLOOKUP(A107, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G107" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A107,"/",2),4),MID(_xlfn.TEXTAFTER(A107,"/",2),6,2),MID(_xlfn.TEXTAFTER(A107,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G107" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
       </c>
       <c r="H107" s="40">
         <f>TRUE()</f>
@@ -18570,9 +18685,10 @@
         <f>IFERROR(VLOOKUP(A108, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G108" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A108,"/",2),4),MID(_xlfn.TEXTAFTER(A108,"/",2),6,2),MID(_xlfn.TEXTAFTER(A108,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G108" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
       </c>
       <c r="H108" s="40">
         <f>TRUE()</f>
@@ -18723,9 +18839,10 @@
         <f>IFERROR(VLOOKUP(A109, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G109" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A109,"/",2),4),MID(_xlfn.TEXTAFTER(A109,"/",2),6,2),MID(_xlfn.TEXTAFTER(A109,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G109" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
       </c>
       <c r="H109" s="40">
         <f>TRUE()</f>
@@ -18876,9 +18993,10 @@
         <f>IFERROR(VLOOKUP(A110, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G110" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A110,"/",2),4),MID(_xlfn.TEXTAFTER(A110,"/",2),6,2),MID(_xlfn.TEXTAFTER(A110,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G110" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
       </c>
       <c r="H110" s="40">
         <f>TRUE()</f>
@@ -19024,9 +19142,10 @@
         <f>IFERROR(VLOOKUP(A111, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G111" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A111,"/",2),4),MID(_xlfn.TEXTAFTER(A111,"/",2),6,2),MID(_xlfn.TEXTAFTER(A111,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G111" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
       </c>
       <c r="H111" s="40">
         <f>FALSE()</f>
@@ -19167,9 +19286,10 @@
         <f>IFERROR(VLOOKUP(A112, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G112" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A112,"/",2),4),MID(_xlfn.TEXTAFTER(A112,"/",2),6,2),MID(_xlfn.TEXTAFTER(A112,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G112" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
       </c>
       <c r="H112" s="40">
         <f>FALSE()</f>
@@ -19320,9 +19440,10 @@
         <f>IFERROR(VLOOKUP(A113, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G113" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A113,"/",2),4),MID(_xlfn.TEXTAFTER(A113,"/",2),6,2),MID(_xlfn.TEXTAFTER(A113,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G113" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
       </c>
       <c r="H113" s="40">
         <f>FALSE()</f>
@@ -19473,9 +19594,10 @@
         <f>IFERROR(VLOOKUP(A114, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G114" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A114,"/",2),4),MID(_xlfn.TEXTAFTER(A114,"/",2),6,2),MID(_xlfn.TEXTAFTER(A114,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G114" s="61" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
       </c>
       <c r="H114" s="40">
         <f>FALSE()</f>
@@ -19626,9 +19748,10 @@
         <f>IFERROR(VLOOKUP(A115, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G115" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A115,"/",2),4),MID(_xlfn.TEXTAFTER(A115,"/",2),6,2),MID(_xlfn.TEXTAFTER(A115,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G115" s="61" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
       </c>
       <c r="H115" s="40">
         <f>FALSE()</f>
@@ -19772,9 +19895,10 @@
       </c>
       <c r="E116" s="40" t="n"/>
       <c r="F116" s="40" t="n"/>
-      <c r="G116" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A116,"/",2),4),MID(_xlfn.TEXTAFTER(A116,"/",2),6,2),MID(_xlfn.TEXTAFTER(A116,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G116" s="61" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
       </c>
       <c r="H116" s="40">
         <f>FALSE()</f>
@@ -19952,9 +20076,10 @@
         <f>IFERROR(VLOOKUP(A117, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G117" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A117,"/",2),4),MID(_xlfn.TEXTAFTER(A117,"/",2),6,2),MID(_xlfn.TEXTAFTER(A117,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G117" s="61" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
       </c>
       <c r="H117" s="40">
         <f>TRUE()</f>
@@ -20105,9 +20230,10 @@
         <f>IFERROR(VLOOKUP(A118, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G118" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A118,"/",2),4),MID(_xlfn.TEXTAFTER(A118,"/",2),6,2),MID(_xlfn.TEXTAFTER(A118,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G118" s="61" t="inlineStr">
+        <is>
+          <t>2015-07-13</t>
+        </is>
       </c>
       <c r="H118" s="40">
         <f>TRUE()</f>
@@ -20258,9 +20384,10 @@
         <f>IFERROR(VLOOKUP(A119, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G119" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A119,"/",2),4),MID(_xlfn.TEXTAFTER(A119,"/",2),6,2),MID(_xlfn.TEXTAFTER(A119,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G119" s="61" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
       </c>
       <c r="H119" s="40">
         <f>TRUE()</f>
@@ -20411,9 +20538,10 @@
         <f>IFERROR(VLOOKUP(A120, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G120" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A120,"/",2),4),MID(_xlfn.TEXTAFTER(A120,"/",2),6,2),MID(_xlfn.TEXTAFTER(A120,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G120" s="61" t="inlineStr">
+        <is>
+          <t>2015-07-15</t>
+        </is>
       </c>
       <c r="H120" s="40">
         <f>TRUE()</f>
@@ -20564,9 +20692,10 @@
         <f>IFERROR(VLOOKUP(A121, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G121" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A121,"/",2),4),MID(_xlfn.TEXTAFTER(A121,"/",2),6,2),MID(_xlfn.TEXTAFTER(A121,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G121" s="61" t="inlineStr">
+        <is>
+          <t>2015-07-16</t>
+        </is>
       </c>
       <c r="H121" s="40">
         <f>TRUE()</f>
@@ -20717,9 +20846,10 @@
         <f>IFERROR(VLOOKUP(A122, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G122" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A122,"/",2),4),MID(_xlfn.TEXTAFTER(A122,"/",2),6,2),MID(_xlfn.TEXTAFTER(A122,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G122" s="61" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
       </c>
       <c r="H122" s="40">
         <f>TRUE()</f>
@@ -20870,9 +21000,10 @@
         <f>IFERROR(VLOOKUP(A123, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G123" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A123,"/",2),4),MID(_xlfn.TEXTAFTER(A123,"/",2),6,2),MID(_xlfn.TEXTAFTER(A123,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G123" s="61" t="inlineStr">
+        <is>
+          <t>2018-06-09</t>
+        </is>
       </c>
       <c r="H123" s="40">
         <f>FALSE()</f>
@@ -21023,9 +21154,10 @@
         <f>IFERROR(VLOOKUP(A124, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G124" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A124,"/",2),4),MID(_xlfn.TEXTAFTER(A124,"/",2),6,2),MID(_xlfn.TEXTAFTER(A124,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G124" s="61" t="inlineStr">
+        <is>
+          <t>2019-08-13</t>
+        </is>
       </c>
       <c r="H124" s="40">
         <f>FALSE()</f>
@@ -21161,9 +21293,10 @@
         <f>IFERROR(VLOOKUP(A125, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G125" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A125,"/",2),4),MID(_xlfn.TEXTAFTER(A125,"/",2),6,2),MID(_xlfn.TEXTAFTER(A125,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G125" s="61" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
       </c>
       <c r="H125" s="40">
         <f>FALSE()</f>
@@ -21299,9 +21432,10 @@
         <f>IFERROR(VLOOKUP(A126, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G126" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A126,"/",2),4),MID(_xlfn.TEXTAFTER(A126,"/",2),6,2),MID(_xlfn.TEXTAFTER(A126,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G126" s="61" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
       </c>
       <c r="H126" s="40">
         <f>FALSE()</f>
@@ -21437,9 +21571,10 @@
         <f>IFERROR(VLOOKUP(A127, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G127" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A127,"/",2),4),MID(_xlfn.TEXTAFTER(A127,"/",2),6,2),MID(_xlfn.TEXTAFTER(A127,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G127" s="61" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
       </c>
       <c r="H127" s="40">
         <f>FALSE()</f>
@@ -21575,9 +21710,10 @@
         <f>IFERROR(VLOOKUP(A128, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G128" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A128,"/",2),4),MID(_xlfn.TEXTAFTER(A128,"/",2),6,2),MID(_xlfn.TEXTAFTER(A128,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G128" s="61" t="inlineStr">
+        <is>
+          <t>2020-06-19</t>
+        </is>
       </c>
       <c r="H128" s="40">
         <f>FALSE()</f>
@@ -21713,9 +21849,10 @@
         <f>IFERROR(VLOOKUP(A129, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G129" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A129,"/",2),4),MID(_xlfn.TEXTAFTER(A129,"/",2),6,2),MID(_xlfn.TEXTAFTER(A129,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G129" s="61" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
       </c>
       <c r="H129" s="40">
         <f>FALSE()</f>
@@ -21856,9 +21993,10 @@
         <f>IFERROR(VLOOKUP(A130, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G130" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A130,"/",2),4),MID(_xlfn.TEXTAFTER(A130,"/",2),6,2),MID(_xlfn.TEXTAFTER(A130,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G130" s="61" t="inlineStr">
+        <is>
+          <t>2021-01-04</t>
+        </is>
       </c>
       <c r="H130" s="40">
         <f>TRUE()</f>
@@ -22009,9 +22147,10 @@
         <f>IFERROR(VLOOKUP(A131, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G131" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A131,"/",2),4),MID(_xlfn.TEXTAFTER(A131,"/",2),6,2),MID(_xlfn.TEXTAFTER(A131,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G131" s="61" t="inlineStr">
+        <is>
+          <t>2021-01-11</t>
+        </is>
       </c>
       <c r="H131" s="40">
         <f>TRUE()</f>
@@ -22162,9 +22301,10 @@
         <f>IFERROR(VLOOKUP(A132, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G132" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A132,"/",2),4),MID(_xlfn.TEXTAFTER(A132,"/",2),6,2),MID(_xlfn.TEXTAFTER(A132,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G132" s="61" t="inlineStr">
+        <is>
+          <t>2021-01-18</t>
+        </is>
       </c>
       <c r="H132" s="40">
         <f>TRUE()</f>
@@ -22315,9 +22455,10 @@
         <f>IFERROR(VLOOKUP(A133, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G133" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A133,"/",2),4),MID(_xlfn.TEXTAFTER(A133,"/",2),6,2),MID(_xlfn.TEXTAFTER(A133,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G133" s="61" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
       </c>
       <c r="H133" s="40">
         <f>TRUE()</f>
@@ -22468,9 +22609,10 @@
         <f>IFERROR(VLOOKUP(A134, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G134" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A134,"/",2),4),MID(_xlfn.TEXTAFTER(A134,"/",2),6,2),MID(_xlfn.TEXTAFTER(A134,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G134" s="61" t="inlineStr">
+        <is>
+          <t>2021-04-05</t>
+        </is>
       </c>
       <c r="H134" s="40">
         <f>TRUE()</f>
@@ -22621,9 +22763,10 @@
         <f>IFERROR(VLOOKUP(A135, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G135" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A135,"/",2),4),MID(_xlfn.TEXTAFTER(A135,"/",2),6,2),MID(_xlfn.TEXTAFTER(A135,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G135" s="61" t="inlineStr">
+        <is>
+          <t>2021-04-12</t>
+        </is>
       </c>
       <c r="H135" s="40">
         <f>TRUE()</f>
@@ -22774,9 +22917,10 @@
         <f>IFERROR(VLOOKUP(A136, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G136" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A136,"/",2),4),MID(_xlfn.TEXTAFTER(A136,"/",2),6,2),MID(_xlfn.TEXTAFTER(A136,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G136" s="61" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
       </c>
       <c r="H136" s="40">
         <f>TRUE()</f>
@@ -22927,9 +23071,10 @@
         <f>IFERROR(VLOOKUP(A137, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G137" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A137,"/",2),4),MID(_xlfn.TEXTAFTER(A137,"/",2),6,2),MID(_xlfn.TEXTAFTER(A137,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G137" s="61" t="inlineStr">
+        <is>
+          <t>2021-05-31</t>
+        </is>
       </c>
       <c r="H137" s="40">
         <f>TRUE()</f>
@@ -23080,9 +23225,10 @@
         <f>IFERROR(VLOOKUP(A138, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G138" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A138,"/",2),4),MID(_xlfn.TEXTAFTER(A138,"/",2),6,2),MID(_xlfn.TEXTAFTER(A138,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G138" s="61" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
       </c>
       <c r="H138" s="40">
         <f>TRUE()</f>
@@ -23233,9 +23379,10 @@
         <f>IFERROR(VLOOKUP(A139, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G139" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A139,"/",2),4),MID(_xlfn.TEXTAFTER(A139,"/",2),6,2),MID(_xlfn.TEXTAFTER(A139,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G139" s="61" t="inlineStr">
+        <is>
+          <t>2021-06-14</t>
+        </is>
       </c>
       <c r="H139" s="40">
         <f>TRUE()</f>
@@ -23386,9 +23533,10 @@
         <f>IFERROR(VLOOKUP(A140, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G140" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A140,"/",2),4),MID(_xlfn.TEXTAFTER(A140,"/",2),6,2),MID(_xlfn.TEXTAFTER(A140,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G140" s="61" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
       </c>
       <c r="H140" s="40">
         <f>TRUE()</f>
@@ -23539,9 +23687,10 @@
         <f>IFERROR(VLOOKUP(A141, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G141" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A141,"/",2),4),MID(_xlfn.TEXTAFTER(A141,"/",2),6,2),MID(_xlfn.TEXTAFTER(A141,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G141" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
       </c>
       <c r="H141" s="40">
         <f>TRUE()</f>
@@ -23692,9 +23841,10 @@
         <f>IFERROR(VLOOKUP(A142, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G142" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A142,"/",2),4),MID(_xlfn.TEXTAFTER(A142,"/",2),6,2),MID(_xlfn.TEXTAFTER(A142,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G142" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
       </c>
       <c r="H142" s="40">
         <f>TRUE()</f>
@@ -23845,9 +23995,10 @@
         <f>IFERROR(VLOOKUP(A143, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G143" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A143,"/",2),4),MID(_xlfn.TEXTAFTER(A143,"/",2),6,2),MID(_xlfn.TEXTAFTER(A143,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G143" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
       </c>
       <c r="H143" s="40">
         <f>TRUE()</f>
@@ -23998,9 +24149,10 @@
         <f>IFERROR(VLOOKUP(A144, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G144" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A144,"/",2),4),MID(_xlfn.TEXTAFTER(A144,"/",2),6,2),MID(_xlfn.TEXTAFTER(A144,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G144" s="61" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
       </c>
       <c r="H144" s="40">
         <f>TRUE()</f>
@@ -24151,9 +24303,10 @@
         <f>IFERROR(VLOOKUP(A145, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G145" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A145,"/",2),4),MID(_xlfn.TEXTAFTER(A145,"/",2),6,2),MID(_xlfn.TEXTAFTER(A145,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G145" s="61" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
       </c>
       <c r="H145" s="40">
         <f>TRUE()</f>
@@ -24304,9 +24457,10 @@
         <f>IFERROR(VLOOKUP(A146, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G146" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A146,"/",2),4),MID(_xlfn.TEXTAFTER(A146,"/",2),6,2),MID(_xlfn.TEXTAFTER(A146,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G146" s="61" t="inlineStr">
+        <is>
+          <t>2021-11-29</t>
+        </is>
       </c>
       <c r="H146" s="40">
         <f>TRUE()</f>
@@ -24457,9 +24611,10 @@
         <f>IFERROR(VLOOKUP(A147, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G147" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A147,"/",2),4),MID(_xlfn.TEXTAFTER(A147,"/",2),6,2),MID(_xlfn.TEXTAFTER(A147,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G147" s="61" t="inlineStr">
+        <is>
+          <t>2021-12-06</t>
+        </is>
       </c>
       <c r="H147" s="40">
         <f>TRUE()</f>
@@ -24610,9 +24765,10 @@
         <f>IFERROR(VLOOKUP(A148, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G148" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A148,"/",2),4),MID(_xlfn.TEXTAFTER(A148,"/",2),6,2),MID(_xlfn.TEXTAFTER(A148,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G148" s="61" t="inlineStr">
+        <is>
+          <t>2021-12-13</t>
+        </is>
       </c>
       <c r="H148" s="40">
         <f>TRUE()</f>
@@ -24763,9 +24919,10 @@
         <f>IFERROR(VLOOKUP(A149, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G149" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A149,"/",2),4),MID(_xlfn.TEXTAFTER(A149,"/",2),6,2),MID(_xlfn.TEXTAFTER(A149,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G149" s="61" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
       </c>
       <c r="H149" s="40">
         <f>TRUE()</f>
@@ -24916,9 +25073,10 @@
         <f>IFERROR(VLOOKUP(A150, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G150" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A150,"/",2),4),MID(_xlfn.TEXTAFTER(A150,"/",2),6,2),MID(_xlfn.TEXTAFTER(A150,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G150" s="61" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
       </c>
       <c r="H150" s="40">
         <f>TRUE()</f>
@@ -25069,9 +25227,10 @@
         <f>IFERROR(VLOOKUP(A151, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G151" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A151,"/",2),4),MID(_xlfn.TEXTAFTER(A151,"/",2),6,2),MID(_xlfn.TEXTAFTER(A151,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G151" s="61" t="inlineStr">
+        <is>
+          <t>2022-02-21</t>
+        </is>
       </c>
       <c r="H151" s="40">
         <f>TRUE()</f>
@@ -25222,9 +25381,10 @@
         <f>IFERROR(VLOOKUP(A152, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G152" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A152,"/",2),4),MID(_xlfn.TEXTAFTER(A152,"/",2),6,2),MID(_xlfn.TEXTAFTER(A152,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G152" s="61" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
       </c>
       <c r="H152" s="40">
         <f>TRUE()</f>
@@ -25375,9 +25535,10 @@
         <f>IFERROR(VLOOKUP(A153, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G153" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A153,"/",2),4),MID(_xlfn.TEXTAFTER(A153,"/",2),6,2),MID(_xlfn.TEXTAFTER(A153,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G153" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
       </c>
       <c r="H153" s="40">
         <f>TRUE()</f>
@@ -25528,9 +25689,10 @@
         <f>IFERROR(VLOOKUP(A154, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G154" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A154,"/",2),4),MID(_xlfn.TEXTAFTER(A154,"/",2),6,2),MID(_xlfn.TEXTAFTER(A154,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G154" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
       </c>
       <c r="H154" s="40">
         <f>TRUE()</f>
@@ -25681,9 +25843,10 @@
         <f>IFERROR(VLOOKUP(A155, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G155" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A155,"/",2),4),MID(_xlfn.TEXTAFTER(A155,"/",2),6,2),MID(_xlfn.TEXTAFTER(A155,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G155" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
       </c>
       <c r="H155" s="40">
         <f>TRUE()</f>
@@ -25834,9 +25997,10 @@
         <f>IFERROR(VLOOKUP(A156, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G156" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A156,"/",2),4),MID(_xlfn.TEXTAFTER(A156,"/",2),6,2),MID(_xlfn.TEXTAFTER(A156,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G156" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
       </c>
       <c r="H156" s="40">
         <f>TRUE()</f>
@@ -25987,9 +26151,10 @@
         <f>IFERROR(VLOOKUP(A157, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G157" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A157,"/",2),4),MID(_xlfn.TEXTAFTER(A157,"/",2),6,2),MID(_xlfn.TEXTAFTER(A157,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G157" s="61" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
       </c>
       <c r="H157" s="40">
         <f>TRUE()</f>
@@ -26140,9 +26305,10 @@
         <f>IFERROR(VLOOKUP(A158, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G158" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A158,"/",2),4),MID(_xlfn.TEXTAFTER(A158,"/",2),6,2),MID(_xlfn.TEXTAFTER(A158,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G158" s="61" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
       </c>
       <c r="H158" s="40">
         <f>TRUE()</f>
@@ -26293,9 +26459,10 @@
         <f>IFERROR(VLOOKUP(A159, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G159" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A159,"/",2),4),MID(_xlfn.TEXTAFTER(A159,"/",2),6,2),MID(_xlfn.TEXTAFTER(A159,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G159" s="61" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
       </c>
       <c r="H159" s="40">
         <f>TRUE()</f>
@@ -26446,9 +26613,10 @@
         <f>IFERROR(VLOOKUP(A160, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G160" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A160,"/",2),4),MID(_xlfn.TEXTAFTER(A160,"/",2),6,2),MID(_xlfn.TEXTAFTER(A160,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G160" s="61" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
       </c>
       <c r="H160" s="40">
         <f>TRUE()</f>
@@ -26594,9 +26762,10 @@
         <f>IFERROR(VLOOKUP(A161, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G161" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A161,"/",2),4),MID(_xlfn.TEXTAFTER(A161,"/",2),6,2),MID(_xlfn.TEXTAFTER(A161,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G161" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
       </c>
       <c r="H161" s="40">
         <f>TRUE()</f>
@@ -26742,9 +26911,10 @@
         <f>IFERROR(VLOOKUP(A162, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G162" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A162,"/",2),4),MID(_xlfn.TEXTAFTER(A162,"/",2),6,2),MID(_xlfn.TEXTAFTER(A162,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G162" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
       </c>
       <c r="H162" s="40">
         <f>TRUE()</f>
@@ -26890,9 +27060,10 @@
         <f>IFERROR(VLOOKUP(A163, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G163" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A163,"/",2),4),MID(_xlfn.TEXTAFTER(A163,"/",2),6,2),MID(_xlfn.TEXTAFTER(A163,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G163" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
       </c>
       <c r="H163" s="40">
         <f>TRUE()</f>
@@ -27038,9 +27209,10 @@
         <f>IFERROR(VLOOKUP(A164, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G164" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A164,"/",2),4),MID(_xlfn.TEXTAFTER(A164,"/",2),6,2),MID(_xlfn.TEXTAFTER(A164,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G164" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
       </c>
       <c r="H164" s="40">
         <f>TRUE()</f>
@@ -27186,9 +27358,10 @@
         <f>IFERROR(VLOOKUP(A165, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G165" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A165,"/",2),4),MID(_xlfn.TEXTAFTER(A165,"/",2),6,2),MID(_xlfn.TEXTAFTER(A165,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G165" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
       </c>
       <c r="H165" s="40">
         <f>TRUE()</f>
@@ -27334,9 +27507,10 @@
         <f>IFERROR(VLOOKUP(A166, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G166" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A166,"/",2),4),MID(_xlfn.TEXTAFTER(A166,"/",2),6,2),MID(_xlfn.TEXTAFTER(A166,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G166" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
       </c>
       <c r="H166" s="40">
         <f>TRUE()</f>
@@ -27482,9 +27656,10 @@
         <f>IFERROR(VLOOKUP(A167, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G167" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A167,"/",2),4),MID(_xlfn.TEXTAFTER(A167,"/",2),6,2),MID(_xlfn.TEXTAFTER(A167,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G167" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
       </c>
       <c r="H167" s="40">
         <f>TRUE()</f>
@@ -27630,9 +27805,10 @@
         <f>IFERROR(VLOOKUP(A168, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G168" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A168,"/",2),4),MID(_xlfn.TEXTAFTER(A168,"/",2),6,2),MID(_xlfn.TEXTAFTER(A168,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G168" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
       </c>
       <c r="H168" s="40">
         <f>TRUE()</f>
@@ -27778,9 +27954,10 @@
         <f>IFERROR(VLOOKUP(A169, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G169" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A169,"/",2),4),MID(_xlfn.TEXTAFTER(A169,"/",2),6,2),MID(_xlfn.TEXTAFTER(A169,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G169" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
       </c>
       <c r="H169" s="40">
         <f>TRUE()</f>
@@ -27927,9 +28104,10 @@
           <t>proceso ETL básico</t>
         </is>
       </c>
-      <c r="G170" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A170,"/",2),4),MID(_xlfn.TEXTAFTER(A170,"/",2),6,2),MID(_xlfn.TEXTAFTER(A170,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G170" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
       </c>
       <c r="H170" s="40">
         <f>TRUE()</f>
@@ -28075,9 +28253,10 @@
         <f>IFERROR(VLOOKUP(A171, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G171" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A171,"/",2),4),MID(_xlfn.TEXTAFTER(A171,"/",2),6,2),MID(_xlfn.TEXTAFTER(A171,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G171" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
       </c>
       <c r="H171" s="40">
         <f>TRUE()</f>
@@ -28223,9 +28402,10 @@
         <f>IFERROR(VLOOKUP(A172, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G172" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A172,"/",2),4),MID(_xlfn.TEXTAFTER(A172,"/",2),6,2),MID(_xlfn.TEXTAFTER(A172,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G172" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
       </c>
       <c r="H172" s="40">
         <f>TRUE()</f>
@@ -28371,9 +28551,10 @@
         <f>IFERROR(VLOOKUP(A173, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G173" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A173,"/",2),4),MID(_xlfn.TEXTAFTER(A173,"/",2),6,2),MID(_xlfn.TEXTAFTER(A173,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G173" s="61" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
       </c>
       <c r="H173" s="40">
         <f>TRUE()</f>
@@ -28519,9 +28700,10 @@
         <f>IFERROR(VLOOKUP(A174, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G174" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A174,"/",2),4),MID(_xlfn.TEXTAFTER(A174,"/",2),6,2),MID(_xlfn.TEXTAFTER(A174,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G174" s="61" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
       </c>
       <c r="H174" s="40">
         <f>TRUE()</f>
@@ -28667,9 +28849,10 @@
         <f>IFERROR(VLOOKUP(A175, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G175" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A175,"/",2),4),MID(_xlfn.TEXTAFTER(A175,"/",2),6,2),MID(_xlfn.TEXTAFTER(A175,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G175" s="61" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
       </c>
       <c r="H175" s="40">
         <f>TRUE()</f>
@@ -28816,9 +28999,10 @@
           <t>columnas y medidas calculadas</t>
         </is>
       </c>
-      <c r="G176" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A176,"/",2),4),MID(_xlfn.TEXTAFTER(A176,"/",2),6,2),MID(_xlfn.TEXTAFTER(A176,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G176" s="61" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
       </c>
       <c r="H176" s="40">
         <f>TRUE()</f>
@@ -28964,9 +29148,10 @@
         <f>IFERROR(VLOOKUP(A177, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G177" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A177,"/",2),4),MID(_xlfn.TEXTAFTER(A177,"/",2),6,2),MID(_xlfn.TEXTAFTER(A177,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G177" s="61" t="inlineStr">
+        <is>
+          <t>2022-10-24</t>
+        </is>
       </c>
       <c r="H177" s="40">
         <f>TRUE()</f>
@@ -29117,9 +29302,10 @@
         <f>IFERROR(VLOOKUP(A178, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G178" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A178,"/",2),4),MID(_xlfn.TEXTAFTER(A178,"/",2),6,2),MID(_xlfn.TEXTAFTER(A178,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G178" s="61" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
       </c>
       <c r="H178" s="40">
         <f>TRUE()</f>
@@ -29270,9 +29456,10 @@
         <f>IFERROR(VLOOKUP(A179, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G179" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A179,"/",2),4),MID(_xlfn.TEXTAFTER(A179,"/",2),6,2),MID(_xlfn.TEXTAFTER(A179,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G179" s="61" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
       </c>
       <c r="H179" s="40">
         <f>TRUE()</f>
@@ -29423,9 +29610,10 @@
         <f>IFERROR(VLOOKUP(A180, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G180" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A180,"/",2),4),MID(_xlfn.TEXTAFTER(A180,"/",2),6,2),MID(_xlfn.TEXTAFTER(A180,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G180" s="61" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
       </c>
       <c r="H180" s="40">
         <f>TRUE()</f>
@@ -29576,9 +29764,10 @@
         <f>IFERROR(VLOOKUP(A181, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G181" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A181,"/",2),4),MID(_xlfn.TEXTAFTER(A181,"/",2),6,2),MID(_xlfn.TEXTAFTER(A181,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G181" s="61" t="inlineStr">
+        <is>
+          <t>2022-11-21</t>
+        </is>
       </c>
       <c r="H181" s="40">
         <f>TRUE()</f>
@@ -29729,9 +29918,10 @@
         <f>IFERROR(VLOOKUP(A182, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G182" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A182,"/",2),4),MID(_xlfn.TEXTAFTER(A182,"/",2),6,2),MID(_xlfn.TEXTAFTER(A182,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G182" s="61" t="inlineStr">
+        <is>
+          <t>2022-11-28</t>
+        </is>
       </c>
       <c r="H182" s="40">
         <f>TRUE()</f>
@@ -29882,9 +30072,10 @@
         <f>IFERROR(VLOOKUP(A183, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G183" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A183,"/",2),4),MID(_xlfn.TEXTAFTER(A183,"/",2),6,2),MID(_xlfn.TEXTAFTER(A183,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G183" s="61" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
       </c>
       <c r="H183" s="40">
         <f>TRUE()</f>
@@ -30035,9 +30226,10 @@
         <f>IFERROR(VLOOKUP(A184, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G184" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A184,"/",2),4),MID(_xlfn.TEXTAFTER(A184,"/",2),6,2),MID(_xlfn.TEXTAFTER(A184,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G184" s="61" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
+        </is>
       </c>
       <c r="H184" s="40">
         <f>TRUE()</f>
@@ -30188,9 +30380,10 @@
         <f>IFERROR(VLOOKUP(A185, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G185" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A185,"/",2),4),MID(_xlfn.TEXTAFTER(A185,"/",2),6,2),MID(_xlfn.TEXTAFTER(A185,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G185" s="61" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
       </c>
       <c r="H185" s="40">
         <f>TRUE()</f>
@@ -30341,9 +30534,10 @@
         <f>IFERROR(VLOOKUP(A186, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G186" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A186,"/",2),4),MID(_xlfn.TEXTAFTER(A186,"/",2),6,2),MID(_xlfn.TEXTAFTER(A186,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G186" s="61" t="inlineStr">
+        <is>
+          <t>2022-12-26</t>
+        </is>
       </c>
       <c r="H186" s="40">
         <f>TRUE()</f>
@@ -30494,9 +30688,10 @@
         <f>IFERROR(VLOOKUP(A187, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G187" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A187,"/",2),4),MID(_xlfn.TEXTAFTER(A187,"/",2),6,2),MID(_xlfn.TEXTAFTER(A187,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G187" s="61" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
       </c>
       <c r="H187" s="40">
         <f>TRUE()</f>
@@ -30647,9 +30842,10 @@
         <f>IFERROR(VLOOKUP(A188, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G188" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A188,"/",2),4),MID(_xlfn.TEXTAFTER(A188,"/",2),6,2),MID(_xlfn.TEXTAFTER(A188,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G188" s="61" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
       </c>
       <c r="H188" s="40">
         <f>TRUE()</f>
@@ -30800,9 +30996,10 @@
         <f>IFERROR(VLOOKUP(A189, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G189" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A189,"/",2),4),MID(_xlfn.TEXTAFTER(A189,"/",2),6,2),MID(_xlfn.TEXTAFTER(A189,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G189" s="61" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
       </c>
       <c r="H189" s="40">
         <f>TRUE()</f>
@@ -30953,9 +31150,10 @@
         <f>IFERROR(VLOOKUP(A190, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G190" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A190,"/",2),4),MID(_xlfn.TEXTAFTER(A190,"/",2),6,2),MID(_xlfn.TEXTAFTER(A190,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G190" s="61" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
       </c>
       <c r="H190" s="40">
         <f>TRUE()</f>
@@ -31101,9 +31299,10 @@
         <f>IFERROR(VLOOKUP(A191, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G191" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A191,"/",2),4),MID(_xlfn.TEXTAFTER(A191,"/",2),6,2),MID(_xlfn.TEXTAFTER(A191,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G191" s="61" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
       </c>
       <c r="H191" s="40">
         <f>TRUE()</f>
@@ -31249,9 +31448,10 @@
         <f>IFERROR(VLOOKUP(A192, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G192" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A192,"/",2),4),MID(_xlfn.TEXTAFTER(A192,"/",2),6,2),MID(_xlfn.TEXTAFTER(A192,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G192" s="61" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
       </c>
       <c r="H192" s="40">
         <f>TRUE()</f>
@@ -31397,9 +31597,10 @@
         <f>IFERROR(VLOOKUP(A193, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G193" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A193,"/",2),4),MID(_xlfn.TEXTAFTER(A193,"/",2),6,2),MID(_xlfn.TEXTAFTER(A193,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G193" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
       </c>
       <c r="H193" s="40">
         <f>TRUE()</f>
@@ -31550,9 +31751,10 @@
         <f>IFERROR(VLOOKUP(A194, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G194" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A194,"/",2),4),MID(_xlfn.TEXTAFTER(A194,"/",2),6,2),MID(_xlfn.TEXTAFTER(A194,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G194" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
       </c>
       <c r="H194" s="40">
         <f>FALSE()</f>
@@ -31703,9 +31905,10 @@
         <f>IFERROR(VLOOKUP(A195, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G195" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A195,"/",2),4),MID(_xlfn.TEXTAFTER(A195,"/",2),6,2),MID(_xlfn.TEXTAFTER(A195,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G195" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
       </c>
       <c r="H195" s="40">
         <f>FALSE()</f>
@@ -31856,9 +32059,10 @@
         <f>IFERROR(VLOOKUP(A196, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G196" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A196,"/",2),4),MID(_xlfn.TEXTAFTER(A196,"/",2),6,2),MID(_xlfn.TEXTAFTER(A196,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G196" s="61" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
       </c>
       <c r="H196" s="40">
         <f>FALSE()</f>
@@ -32019,9 +32223,10 @@
         <f>IFERROR(VLOOKUP(A197, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G197" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A197,"/",2),4),MID(_xlfn.TEXTAFTER(A197,"/",2),6,2),MID(_xlfn.TEXTAFTER(A197,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G197" s="61" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
       </c>
       <c r="H197" s="40">
         <f>TRUE()</f>
@@ -32167,9 +32372,10 @@
         <f>IFERROR(VLOOKUP(A198, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G198" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A198,"/",2),4),MID(_xlfn.TEXTAFTER(A198,"/",2),6,2),MID(_xlfn.TEXTAFTER(A198,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G198" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
       </c>
       <c r="H198" s="40">
         <f>TRUE()</f>
@@ -32315,9 +32521,10 @@
         <f>IFERROR(VLOOKUP(A199, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G199" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A199,"/",2),4),MID(_xlfn.TEXTAFTER(A199,"/",2),6,2),MID(_xlfn.TEXTAFTER(A199,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G199" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
       </c>
       <c r="H199" s="40">
         <f>TRUE()</f>
@@ -32463,9 +32670,10 @@
         <f>IFERROR(VLOOKUP(A200, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G200" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A200,"/",2),4),MID(_xlfn.TEXTAFTER(A200,"/",2),6,2),MID(_xlfn.TEXTAFTER(A200,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G200" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
       </c>
       <c r="H200" s="40">
         <f>TRUE()</f>
@@ -32611,9 +32819,10 @@
         <f>IFERROR(VLOOKUP(A201, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G201" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A201,"/",2),4),MID(_xlfn.TEXTAFTER(A201,"/",2),6,2),MID(_xlfn.TEXTAFTER(A201,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G201" s="61" t="inlineStr">
+        <is>
+          <t>2021-07-26</t>
+        </is>
       </c>
       <c r="H201" s="40">
         <f>TRUE()</f>
@@ -32759,9 +32968,10 @@
         <f>IFERROR(VLOOKUP(A202, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G202" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A202,"/",2),4),MID(_xlfn.TEXTAFTER(A202,"/",2),6,2),MID(_xlfn.TEXTAFTER(A202,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G202" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
       </c>
       <c r="H202" s="40">
         <f>TRUE()</f>
@@ -32907,9 +33117,10 @@
         <f>IFERROR(VLOOKUP(A203, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G203" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A203,"/",2),4),MID(_xlfn.TEXTAFTER(A203,"/",2),6,2),MID(_xlfn.TEXTAFTER(A203,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G203" s="61" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
       </c>
       <c r="H203" s="40">
         <f>TRUE()</f>
@@ -33055,9 +33266,10 @@
         <f>IFERROR(VLOOKUP(A204, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G204" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A204,"/",2),4),MID(_xlfn.TEXTAFTER(A204,"/",2),6,2),MID(_xlfn.TEXTAFTER(A204,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G204" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
       </c>
       <c r="H204" s="40">
         <f>FALSE()</f>
@@ -33193,9 +33405,10 @@
         <f>IFERROR(VLOOKUP(A205, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G205" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A205,"/",2),4),MID(_xlfn.TEXTAFTER(A205,"/",2),6,2),MID(_xlfn.TEXTAFTER(A205,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G205" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
       </c>
       <c r="H205" s="40">
         <f>FALSE()</f>
@@ -33331,9 +33544,10 @@
         <f>IFERROR(VLOOKUP(A206, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G206" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A206,"/",2),4),MID(_xlfn.TEXTAFTER(A206,"/",2),6,2),MID(_xlfn.TEXTAFTER(A206,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G206" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
       </c>
       <c r="H206" s="40">
         <f>FALSE()</f>
@@ -33469,9 +33683,10 @@
         <f>IFERROR(VLOOKUP(A207, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G207" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A207,"/",2),4),MID(_xlfn.TEXTAFTER(A207,"/",2),6,2),MID(_xlfn.TEXTAFTER(A207,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G207" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
       </c>
       <c r="H207" s="40">
         <f>FALSE()</f>
@@ -33607,9 +33822,10 @@
         <f>IFERROR(VLOOKUP(A208, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G208" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A208,"/",2),4),MID(_xlfn.TEXTAFTER(A208,"/",2),6,2),MID(_xlfn.TEXTAFTER(A208,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G208" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
       </c>
       <c r="H208" s="40">
         <f>TRUE()</f>
@@ -33755,9 +33971,10 @@
         <f>IFERROR(VLOOKUP(A209, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G209" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A209,"/",2),4),MID(_xlfn.TEXTAFTER(A209,"/",2),6,2),MID(_xlfn.TEXTAFTER(A209,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G209" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
       </c>
       <c r="H209" s="40">
         <f>TRUE()</f>
@@ -33903,9 +34120,10 @@
         <f>IFERROR(VLOOKUP(A210, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G210" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A210,"/",2),4),MID(_xlfn.TEXTAFTER(A210,"/",2),6,2),MID(_xlfn.TEXTAFTER(A210,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G210" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
       </c>
       <c r="H210" s="40">
         <f>FALSE()</f>
@@ -34046,9 +34264,10 @@
         <f>IFERROR(VLOOKUP(A211, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G211" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A211,"/",2),4),MID(_xlfn.TEXTAFTER(A211,"/",2),6,2),MID(_xlfn.TEXTAFTER(A211,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G211" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
       </c>
       <c r="H211" s="40">
         <f>TRUE()</f>
@@ -34199,9 +34418,10 @@
         <f>IFERROR(VLOOKUP(A212, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G212" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A212,"/",2),4),MID(_xlfn.TEXTAFTER(A212,"/",2),6,2),MID(_xlfn.TEXTAFTER(A212,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G212" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
       </c>
       <c r="H212" s="40">
         <f>TRUE()</f>
@@ -34352,9 +34572,10 @@
         <f>IFERROR(VLOOKUP(A213, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G213" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A213,"/",2),4),MID(_xlfn.TEXTAFTER(A213,"/",2),6,2),MID(_xlfn.TEXTAFTER(A213,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G213" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
       </c>
       <c r="H213" s="40">
         <f>TRUE()</f>
@@ -34505,9 +34726,10 @@
         <f>IFERROR(VLOOKUP(A214, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G214" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A214,"/",2),4),MID(_xlfn.TEXTAFTER(A214,"/",2),6,2),MID(_xlfn.TEXTAFTER(A214,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G214" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
       </c>
       <c r="H214" s="40">
         <f>TRUE()</f>
@@ -34658,9 +34880,10 @@
         <f>IFERROR(VLOOKUP(A215, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G215" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A215,"/",2),4),MID(_xlfn.TEXTAFTER(A215,"/",2),6,2),MID(_xlfn.TEXTAFTER(A215,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G215" s="61" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
       </c>
       <c r="H215" s="40">
         <f>TRUE()</f>
@@ -34811,9 +35034,10 @@
         <f>IFERROR(VLOOKUP(A216, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G216" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A216,"/",2),4),MID(_xlfn.TEXTAFTER(A216,"/",2),6,2),MID(_xlfn.TEXTAFTER(A216,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G216" s="61" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
       </c>
       <c r="H216" s="40">
         <f>TRUE()</f>
@@ -34959,9 +35183,10 @@
         <f>IFERROR(VLOOKUP(A217, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G217" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A217,"/",2),4),MID(_xlfn.TEXTAFTER(A217,"/",2),6,2),MID(_xlfn.TEXTAFTER(A217,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G217" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
       </c>
       <c r="H217" s="40">
         <f>FALSE()</f>
@@ -35097,9 +35322,10 @@
         <f>IFERROR(VLOOKUP(A218, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G218" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A218,"/",2),4),MID(_xlfn.TEXTAFTER(A218,"/",2),6,2),MID(_xlfn.TEXTAFTER(A218,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G218" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
       </c>
       <c r="H218" s="40">
         <f>FALSE()</f>
@@ -35235,9 +35461,10 @@
         <f>IFERROR(VLOOKUP(A219, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G219" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A219,"/",2),4),MID(_xlfn.TEXTAFTER(A219,"/",2),6,2),MID(_xlfn.TEXTAFTER(A219,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G219" s="61" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
       </c>
       <c r="H219" s="40">
         <f>TRUE()</f>
@@ -35388,9 +35615,10 @@
         <f>IFERROR(VLOOKUP(A220, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G220" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A220,"/",2),4),MID(_xlfn.TEXTAFTER(A220,"/",2),6,2),MID(_xlfn.TEXTAFTER(A220,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G220" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
       </c>
       <c r="H220" s="40">
         <f>FALSE()</f>
@@ -35541,9 +35769,10 @@
         <f>IFERROR(VLOOKUP(A221, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G221" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A221,"/",2),4),MID(_xlfn.TEXTAFTER(A221,"/",2),6,2),MID(_xlfn.TEXTAFTER(A221,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G221" s="61" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
       </c>
       <c r="H221" s="40">
         <f>FALSE()</f>
@@ -35694,9 +35923,10 @@
         <f>IFERROR(VLOOKUP(A222, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G222" s="40">
-        <f>TEXT(DATE(LEFT(_xlfn.TEXTAFTER(A222,"/",2),4),MID(_xlfn.TEXTAFTER(A222,"/",2),6,2),MID(_xlfn.TEXTAFTER(A222,"/",2),9,2)),"mm/dd/yyyy")</f>
-        <v/>
+      <c r="G222" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
       </c>
       <c r="H222" s="40">
         <f>FALSE()</f>
@@ -35848,9 +36078,9 @@
           <t>Portafolios Excepcionales en HTML, CSS y JS</t>
         </is>
       </c>
-      <c r="G223" s="53" t="inlineStr">
-        <is>
-          <t>04/23/2017</t>
+      <c r="G223" s="62" t="inlineStr">
+        <is>
+          <t>2017-04-23</t>
         </is>
       </c>
       <c r="H223" s="54">
@@ -35977,9 +36207,9 @@
         <f>IFERROR(VLOOKUP(A224, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G224" s="40" t="inlineStr">
-        <is>
-          <t>05/23/2020</t>
+      <c r="G224" s="61" t="inlineStr">
+        <is>
+          <t>2020-05-23</t>
         </is>
       </c>
       <c r="H224" s="40">
@@ -36079,9 +36309,9 @@
         <f>IFERROR(VLOOKUP(A225, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G225" s="40" t="inlineStr">
-        <is>
-          <t>04/22/2022</t>
+      <c r="G225" s="61" t="inlineStr">
+        <is>
+          <t>2022-04-22</t>
         </is>
       </c>
       <c r="H225" s="40">
@@ -36181,9 +36411,9 @@
         <f>IFERROR(VLOOKUP(A226, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G226" s="40" t="inlineStr">
-        <is>
-          <t>06/02/2022</t>
+      <c r="G226" s="61" t="inlineStr">
+        <is>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="H226" s="40">
@@ -36276,9 +36506,9 @@
           <t xml:space="preserve"> crisis y reformas</t>
         </is>
       </c>
-      <c r="G227" s="40" t="inlineStr">
-        <is>
-          <t>05/12/2023</t>
+      <c r="G227" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="H227" s="40">
@@ -36374,9 +36604,9 @@
         <f>IFERROR(VLOOKUP(A228, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G228" s="40" t="inlineStr">
-        <is>
-          <t>01/01/2014</t>
+      <c r="G228" s="61" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="H228" s="40">
@@ -36461,9 +36691,9 @@
         <f>IFERROR(VLOOKUP(A229, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G229" s="40" t="inlineStr">
-        <is>
-          <t>05/16/2023</t>
+      <c r="G229" s="61" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H229" s="40">
@@ -36595,9 +36825,9 @@
         <f>IFERROR(VLOOKUP(A230, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G230" s="40" t="inlineStr">
-        <is>
-          <t>01/07/2014</t>
+      <c r="G230" s="61" t="inlineStr">
+        <is>
+          <t>2014-01-07</t>
         </is>
       </c>
       <c r="H230" s="40">
@@ -36692,9 +36922,9 @@
         <f>IFERROR(VLOOKUP(A231, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G231" s="40" t="inlineStr">
-        <is>
-          <t>01/14/2014</t>
+      <c r="G231" s="61" t="inlineStr">
+        <is>
+          <t>2014-01-14</t>
         </is>
       </c>
       <c r="H231" s="40">
@@ -36789,9 +37019,9 @@
         <f>IFERROR(VLOOKUP(A232, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G232" s="40" t="inlineStr">
-        <is>
-          <t>01/21/2014</t>
+      <c r="G232" s="61" t="inlineStr">
+        <is>
+          <t>2014-01-21</t>
         </is>
       </c>
       <c r="H232" s="40">
@@ -36886,9 +37116,9 @@
         <f>IFERROR(VLOOKUP(A233, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G233" s="40" t="inlineStr">
-        <is>
-          <t>01/28/2014</t>
+      <c r="G233" s="61" t="inlineStr">
+        <is>
+          <t>2014-01-28</t>
         </is>
       </c>
       <c r="H233" s="40">
@@ -36983,9 +37213,9 @@
         <f>IFERROR(VLOOKUP(A234, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G234" s="40" t="inlineStr">
-        <is>
-          <t>02/04/2014</t>
+      <c r="G234" s="61" t="inlineStr">
+        <is>
+          <t>2014-02-04</t>
         </is>
       </c>
       <c r="H234" s="40">
@@ -37080,9 +37310,9 @@
         <f>IFERROR(VLOOKUP(A235, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G235" s="40" t="inlineStr">
-        <is>
-          <t>02/11/2014</t>
+      <c r="G235" s="61" t="inlineStr">
+        <is>
+          <t>2014-02-11</t>
         </is>
       </c>
       <c r="H235" s="40">
@@ -37177,9 +37407,9 @@
         <f>IFERROR(VLOOKUP(A236, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G236" s="40" t="inlineStr">
-        <is>
-          <t>02/18/2014</t>
+      <c r="G236" s="61" t="inlineStr">
+        <is>
+          <t>2014-02-18</t>
         </is>
       </c>
       <c r="H236" s="40">
@@ -37274,9 +37504,9 @@
         <f>IFERROR(VLOOKUP(A237, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G237" s="40" t="inlineStr">
-        <is>
-          <t>02/25/2014</t>
+      <c r="G237" s="61" t="inlineStr">
+        <is>
+          <t>2014-02-25</t>
         </is>
       </c>
       <c r="H237" s="40">
@@ -37372,9 +37602,9 @@
           <t>causas y efectos</t>
         </is>
       </c>
-      <c r="G238" s="40" t="inlineStr">
-        <is>
-          <t>03/01/2014</t>
+      <c r="G238" s="61" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="H238" s="40">
@@ -37469,9 +37699,9 @@
         <f>IFERROR(VLOOKUP(A239, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G239" s="40" t="inlineStr">
-        <is>
-          <t>03/08/2014</t>
+      <c r="G239" s="61" t="inlineStr">
+        <is>
+          <t>2014-03-08</t>
         </is>
       </c>
       <c r="H239" s="40">
@@ -37566,9 +37796,9 @@
         <f>IFERROR(VLOOKUP(A240, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G240" s="40" t="inlineStr">
-        <is>
-          <t>03/15/2014</t>
+      <c r="G240" s="61" t="inlineStr">
+        <is>
+          <t>2014-03-15</t>
         </is>
       </c>
       <c r="H240" s="40">
@@ -37664,9 +37894,9 @@
           <t xml:space="preserve"> tipos y medición</t>
         </is>
       </c>
-      <c r="G241" s="40" t="inlineStr">
-        <is>
-          <t>03/22/2014</t>
+      <c r="G241" s="61" t="inlineStr">
+        <is>
+          <t>2014-03-22</t>
         </is>
       </c>
       <c r="H241" s="40">
@@ -37761,9 +37991,9 @@
         <f>IFERROR(VLOOKUP(A242, #REF!, 3, 0), "")</f>
         <v/>
       </c>
-      <c r="G242" s="40" t="inlineStr">
-        <is>
-          <t>03/29/2014</t>
+      <c r="G242" s="61" t="inlineStr">
+        <is>
+          <t>2014-03-29</t>
         </is>
       </c>
       <c r="H242" s="40">
@@ -37930,8 +38160,10 @@
           <t>Primera Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G244" s="60" t="n">
-        <v>45664</v>
+      <c r="G244" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-07</t>
+        </is>
       </c>
       <c r="J244" s="40" t="inlineStr">
         <is>
@@ -38004,8 +38236,10 @@
           <t>Segunda Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G245" s="60" t="n">
-        <v>45665</v>
+      <c r="G245" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
       </c>
       <c r="J245" s="40" t="inlineStr">
         <is>
@@ -38078,8 +38312,10 @@
           <t>Tercera Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G246" s="60" t="n">
-        <v>45671</v>
+      <c r="G246" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
       </c>
       <c r="J246" s="40" t="inlineStr">
         <is>
@@ -38152,8 +38388,10 @@
           <t>Primera Práctica en word</t>
         </is>
       </c>
-      <c r="G247" s="60" t="n">
-        <v>45672</v>
+      <c r="G247" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
       </c>
       <c r="J247" s="40" t="inlineStr">
         <is>
@@ -38228,8 +38466,10 @@
           <t>Quinta Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G248" s="60" t="n">
-        <v>45679</v>
+      <c r="G248" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
       </c>
       <c r="J248" s="40" t="inlineStr">
         <is>
@@ -38304,8 +38544,10 @@
           <t>Sexta Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G249" s="60" t="n">
-        <v>45686</v>
+      <c r="G249" s="61" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
       </c>
       <c r="J249" s="40" t="inlineStr">
         <is>
@@ -38380,8 +38622,10 @@
           <t>Séptima Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G250" s="60" t="n">
-        <v>45693</v>
+      <c r="G250" s="61" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
       </c>
       <c r="J250" s="40" t="inlineStr">
         <is>
@@ -38456,8 +38700,10 @@
           <t>Octavo Clase en CAU - UNSCH</t>
         </is>
       </c>
-      <c r="G251" s="60" t="n">
-        <v>45700</v>
+      <c r="G251" s="61" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
       </c>
       <c r="J251" s="40" t="inlineStr">
         <is>
@@ -38532,8 +38778,10 @@
           <t>Segunda práctica en word</t>
         </is>
       </c>
-      <c r="G252" s="60" t="n">
-        <v>45707</v>
+      <c r="G252" s="61" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
       </c>
       <c r="J252" s="40" t="inlineStr">
         <is>
@@ -39747,351 +39995,351 @@
       <c r="BG600" s="48" t="n"/>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
+      <c r="A601" s="35" t="inlineStr">
         <is>
           <t>pub_chaska/operating-system/2026-04-23-guia-de-rsync/index.qmd</t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B601" s="35" t="inlineStr">
         <is>
           <t>pub_chaska</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C601" s="35" t="inlineStr">
         <is>
           <t>doc</t>
         </is>
       </c>
-      <c r="D601" t="inlineStr">
+      <c r="D601" s="35" t="inlineStr">
         <is>
           <t>Guía Completa de rsync</t>
         </is>
       </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>12/31/2025</t>
-        </is>
-      </c>
-      <c r="H601" t="b">
+      <c r="G601" s="63" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H601" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="I601" t="inlineStr">
+      <c r="I601" s="35" t="inlineStr">
         <is>
           <t>Positron es un IDE moderno y especializado en ciencia de datos, construido sobre el núcleo open-source de VS Code (Code OSS) y desarrollado por Posit Software. Ofrece soporte nativo para Python y R, consola interactiva avanzada, paneles especializados (Variables, Data Explorer, Plots, Help), integración completa con Quarto y herramientas de asistencia IA. Esta guía completa cubre desde la instalación multiplataforma hasta la configuración avanzada, migración desde VS Code, personalización profunda y mejores prácticas para flujos de trabajo intensivos en análisis de datos, programación estadística y publicación científica reproducible.</t>
         </is>
       </c>
-      <c r="J601" t="inlineStr">
+      <c r="J601" s="35" t="inlineStr">
         <is>
           <t>Guía de Positron IDE; el entorno de desarrollo integrado diseñado específicamente para ciencia de datos con soporte nativo Python/R, paneles interactivos de datos y visualización, Quarto integrado y asistente IA.</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr">
+      <c r="K601" s="35" t="inlineStr">
         <is>
           <t>Rsync</t>
         </is>
       </c>
-      <c r="L601" t="inlineStr">
+      <c r="L601" s="35" t="inlineStr">
         <is>
           <t>operating_system, rsync</t>
         </is>
       </c>
-      <c r="M601" t="inlineStr">
+      <c r="M601" s="35" t="inlineStr">
         <is>
           <t>Operating System</t>
         </is>
       </c>
-      <c r="N601" t="inlineStr">
+      <c r="N601" s="35" t="inlineStr">
         <is>
           <t>featured.png</t>
         </is>
       </c>
-      <c r="O601" t="b">
+      <c r="O601" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="Q601" t="inlineStr">
+      <c r="Q601" s="35" t="inlineStr">
         <is>
           <t>article-journal</t>
         </is>
       </c>
-      <c r="R601" t="inlineStr">
+      <c r="R601" s="35" t="inlineStr">
         <is>
           <t>Edison Achalma</t>
         </is>
       </c>
-      <c r="S601" t="inlineStr">
+      <c r="S601" s="35" t="inlineStr">
         <is>
           <t>https://chaska-x.netlify.app/operating-system/2023-02-16-guia-de-git-y-github/index.pdf</t>
         </is>
       </c>
-      <c r="T601" t="b">
+      <c r="T601" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="AB601" t="n">
+      <c r="AB601" s="35" t="n">
         <v>2025</v>
       </c>
-      <c r="AC601" t="inlineStr">
+      <c r="AC601" s="35" t="inlineStr">
         <is>
           <t>All rights reserved</t>
         </is>
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
+      <c r="A602" s="35" t="inlineStr">
         <is>
           <t>pub_chaska/operating-system/2021-10-21-scrcpy/index.qmd</t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B602" s="35" t="inlineStr">
         <is>
           <t>pub_chaska</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C602" s="35" t="inlineStr">
         <is>
           <t>doc</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr">
+      <c r="D602" s="35" t="inlineStr">
         <is>
           <t>Scrcpy</t>
         </is>
       </c>
-      <c r="G602" t="inlineStr">
-        <is>
-          <t>10/21/2021</t>
-        </is>
-      </c>
-      <c r="H602" t="b">
+      <c r="G602" s="63" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="H602" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="I602" t="inlineStr">
+      <c r="I602" s="35" t="inlineStr">
         <is>
           <t>Este abstract será actualizado una vez que se complete el contenido final del artículo.</t>
         </is>
       </c>
-      <c r="J602" t="inlineStr">
+      <c r="J602" s="35" t="inlineStr">
         <is>
           <t>Cómo ejecutar aplicaciones Android (APK) directamente en Windows 11 mediante el subsistema WSA, instalación y solución de problemas comunes.</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr">
+      <c r="K602" s="35" t="inlineStr">
         <is>
           <t>keyword1, keyword2</t>
         </is>
       </c>
-      <c r="L602" t="inlineStr">
+      <c r="L602" s="35" t="inlineStr">
         <is>
           <t>operating_system, windows, apk</t>
         </is>
       </c>
-      <c r="M602" t="inlineStr">
+      <c r="M602" s="35" t="inlineStr">
         <is>
           <t>Operating System</t>
         </is>
       </c>
-      <c r="N602" t="inlineStr">
+      <c r="N602" s="35" t="inlineStr">
         <is>
           <t>../featured.jpg</t>
         </is>
       </c>
-      <c r="O602" t="b">
+      <c r="O602" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="Q602" t="inlineStr">
+      <c r="Q602" s="35" t="inlineStr">
         <is>
           <t>article-journal</t>
         </is>
       </c>
-      <c r="R602" t="inlineStr">
+      <c r="R602" s="35" t="inlineStr">
         <is>
           <t>Edison Achalma</t>
         </is>
       </c>
-      <c r="S602" t="inlineStr">
+      <c r="S602" s="35" t="inlineStr">
         <is>
           <t>https://chaska-x.netlify.app/operating-system/2021-10-21-usando-apk-en-windown-11/index.pdf</t>
         </is>
       </c>
-      <c r="T602" t="b">
+      <c r="T602" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="AB602" t="n">
+      <c r="AB602" s="35" t="n">
         <v>2021</v>
       </c>
-      <c r="AC602" t="inlineStr">
+      <c r="AC602" s="35" t="inlineStr">
         <is>
           <t>All rights reserved</t>
         </is>
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
+      <c r="A603" s="35" t="inlineStr">
         <is>
           <t>pub_methodica/posts/2026-01-02-configuracion-de-quarto-yml/index.qmd</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B603" s="35" t="inlineStr">
         <is>
           <t>pub_methodica</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C603" s="35" t="inlineStr">
         <is>
           <t>doc</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr">
+      <c r="D603" s="35" t="inlineStr">
         <is>
           <t>Configuración de `_quarto.yml` para Proyectos Quarto</t>
         </is>
       </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>01/02/2026</t>
-        </is>
-      </c>
-      <c r="H603" t="b">
+      <c r="G603" s="63" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="H603" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="I603" t="inlineStr">
+      <c r="I603" s="35" t="inlineStr">
         <is>
           <t>Esta publiación proporciona una guía sobre la configuración del archivo _quarto.yml en proyectos Quarto, que actúa como el archivo principal para definir opciones globales aplicables a sitios web académicos, libros o proyectos simples. Se explica su diferencia con _metadata.yml, destacando el alcance global del primero frente al directorio específico del segundo. Se detallan las funciones principales, como el control del tipo de proyecto, estructura del sitio (navegación, footer, sidebar), apariencia (temas, CSS), metadatos SEO, integración de herramientas externas (Google Analytics, comentarios) y formatos de salida (HTML, PDF, DOCX). Se analiza la jerarquía de configuración, con énfasis en la prioridad (del front-matter del documento a los valores por defecto) y la herencia/combinación de opciones. La estructura del archivo se desglosa en secciones clave; project (tipo, output-dir, resources), website (título, navbar, sidebar, footer, anuncios, Open Graph, Twitter Cards), y format (opciones por formato). Además, se incluyen configuraciones avanzadas, un análisis de una configuración ejemplo, sugerencias de optimización, casos de uso prácticos (blog académico, documentación técnica, portfolio), mejores prácticas, troubleshooting y comandos útiles. El objetivo es capacitar a investigadores y desarrolladores para crear sitios web académicos y profesionales eficientes con Quarto, priorizando accesibilidad, SEO y privacidad (RGPD). Se enfatiza la validación YAML, testing y recursos adicionales para una implementación óptima.</t>
         </is>
       </c>
-      <c r="J603" t="inlineStr">
+      <c r="J603" s="35" t="inlineStr">
         <is>
           <t>_quarto.yml es el archivo de configuración principal de un proyecto Quarto. Define las opciones globales que se aplicarán a todo el sitio web, libro o proyecto.</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr">
+      <c r="K603" s="35" t="inlineStr">
         <is>
           <t>Quarto, _metadata.yml, Metadatos compartidos</t>
         </is>
       </c>
-      <c r="L603" t="inlineStr">
+      <c r="L603" s="35" t="inlineStr">
         <is>
           <t>metodologia_investigacion, quarto, _quarto.yml</t>
         </is>
       </c>
-      <c r="M603" t="inlineStr">
+      <c r="M603" s="35" t="inlineStr">
         <is>
           <t>Metodología de Investigación</t>
         </is>
       </c>
-      <c r="N603" t="inlineStr">
+      <c r="N603" s="35" t="inlineStr">
         <is>
           <t>../featured.jpg</t>
         </is>
       </c>
-      <c r="O603" t="b">
+      <c r="O603" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="Q603" t="inlineStr">
+      <c r="Q603" s="35" t="inlineStr">
         <is>
           <t>article-journal</t>
         </is>
       </c>
-      <c r="R603" t="inlineStr">
+      <c r="R603" s="35" t="inlineStr">
         <is>
           <t>Edison Achalma</t>
         </is>
       </c>
-      <c r="T603" t="b">
+      <c r="T603" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="AB603" t="n">
+      <c r="AB603" s="35" t="n">
         <v>2026</v>
       </c>
-      <c r="AC603" t="inlineStr">
+      <c r="AC603" s="35" t="inlineStr">
         <is>
           <t>All rights reserved</t>
         </is>
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr">
+      <c r="A604" s="35" t="inlineStr">
         <is>
           <t>pub_numerus-scriptum/r/2020-06-10-012-configurar-entorno-virtual-r/index.qmd</t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B604" s="35" t="inlineStr">
         <is>
           <t>pub_numerus-scriptum</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C604" s="35" t="inlineStr">
         <is>
           <t>man</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr">
+      <c r="D604" s="35" t="inlineStr">
         <is>
           <t>Guía completa de entornos virtuales en R con RStudio (renv)</t>
         </is>
       </c>
-      <c r="G604" t="inlineStr">
-        <is>
-          <t>06/10/2020</t>
-        </is>
-      </c>
-      <c r="H604" t="b">
+      <c r="G604" s="63" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
+      </c>
+      <c r="H604" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="I604" t="inlineStr">
+      <c r="I604" s="35" t="inlineStr">
         <is>
           <t>Este abstract será actualizado una vez que se complete el contenido final del artículo.</t>
         </is>
       </c>
-      <c r="J604" t="inlineStr">
+      <c r="J604" s="35" t="inlineStr">
         <is>
           <t>Panorama de las fortalezas de R en estadística, visualización y ciencia de datos frente a otros lenguajes.</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr">
+      <c r="K604" s="35" t="inlineStr">
         <is>
           <t>keyword1, keyword2</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr">
+      <c r="L604" s="35" t="inlineStr">
         <is>
           <t>r, rstudio, ventajas_r</t>
         </is>
       </c>
-      <c r="M604" t="inlineStr">
+      <c r="M604" s="35" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N604" t="inlineStr">
+      <c r="N604" s="35" t="inlineStr">
         <is>
           <t>../featured.jpg</t>
         </is>
       </c>
-      <c r="O604" t="b">
+      <c r="O604" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="Q604" t="inlineStr">
+      <c r="Q604" s="35" t="inlineStr">
         <is>
           <t>article-journal</t>
         </is>
       </c>
-      <c r="R604" t="inlineStr">
+      <c r="R604" s="35" t="inlineStr">
         <is>
           <t>Edison Achalma</t>
         </is>
       </c>
-      <c r="S604" t="inlineStr">
+      <c r="S604" s="35" t="inlineStr">
         <is>
           <t>https://numerus-scriptum.netlify.app/r/2020-06-10-012-que-ofrece-r/index.pdf</t>
         </is>
       </c>
-      <c r="T604" t="b">
+      <c r="T604" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="AB604" t="n">
+      <c r="AB604" s="35" t="n">
         <v>2020</v>
       </c>
-      <c r="AC604" t="inlineStr">
+      <c r="AC604" s="35" t="inlineStr">
         <is>
           <t>All rights reserved</t>
         </is>

--- a/backend/script_metadata_manager/excel_databases/quarto_metadata.xlsx
+++ b/backend/script_metadata_manager/excel_databases/quarto_metadata.xlsx
@@ -3342,7 +3342,7 @@
       </c>
       <c r="G7" s="61" t="inlineStr">
         <is>
-          <t>2017-12-30</t>
+          <t>2017-05-11</t>
         </is>
       </c>
       <c r="H7" s="40">
